--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A078BBE-D8ED-484B-B1A3-60EED3221DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713C1F66-9E66-0741-90E5-35032EA6DFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="146">
   <si>
     <t>Event</t>
   </si>
@@ -451,9 +451,6 @@
     <t>IA</t>
   </si>
   <si>
-    <t>MÍT</t>
-  </si>
-  <si>
     <t>NB</t>
   </si>
   <si>
@@ -466,9 +463,6 @@
     <t>KP</t>
   </si>
   <si>
-    <t>Barna dans</t>
-  </si>
-  <si>
     <t>UpT</t>
   </si>
   <si>
@@ -482,9 +476,6 @@
   </si>
   <si>
     <t>HT</t>
-  </si>
-  <si>
-    <t>KV</t>
   </si>
   <si>
     <t>DP</t>
@@ -571,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -583,7 +574,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
@@ -1084,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="7">
         <v>46113</v>
@@ -1169,7 +1159,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J6" s="7">
         <v>46114</v>
@@ -1212,7 +1202,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" s="7">
         <v>46116</v>
@@ -1643,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="7">
         <v>46127</v>
@@ -1707,7 +1697,7 @@
         <v>128</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="6" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1715,30 +1705,31 @@
       </c>
       <c r="E19" s="6">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F19" s="6" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G19" s="6">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H19" s="6">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="7">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="K19" s="8">
-        <v>0.6875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L19" s="8">
-        <v>0.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1746,10 +1737,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1757,30 +1748,31 @@
       </c>
       <c r="E20" s="6">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F20" s="6" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G20" s="6">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H20" s="6">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J20" s="7">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="K20" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L20" s="8">
-        <v>0.875</v>
+        <v>0.70833333333333337</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1788,7 +1780,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>6</v>
@@ -1813,27 +1805,27 @@
         <v>0</v>
       </c>
       <c r="I21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="K21" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="L21" s="8">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22" s="6" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1841,41 +1833,42 @@
       </c>
       <c r="E22" s="6">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F22" s="6" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G22" s="6">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H22" s="6">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J22" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="K22" s="8">
-        <v>0.625</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="6" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="6" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1883,30 +1876,30 @@
       </c>
       <c r="E23" s="6">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F23" s="6" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" s="6">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6">
         <v>1</v>
       </c>
       <c r="J23" s="7">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="K23" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="L23" s="8">
-        <v>0.91666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1914,10 +1907,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" s="6" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1925,31 +1918,30 @@
       </c>
       <c r="E24" s="6">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F24" s="6" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G24" s="6">
-        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H24" s="6">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="7">
-        <v>46129</v>
+        <v>46137</v>
       </c>
       <c r="K24" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L24" s="8">
-        <v>0.91666666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1957,10 +1949,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="6" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1968,31 +1960,30 @@
       </c>
       <c r="E25" s="6">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F25" s="6" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G25" s="6">
-        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H25" s="6">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="7">
-        <v>46130</v>
+        <v>46141</v>
       </c>
       <c r="K25" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L25" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -2000,10 +1991,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="6" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2011,28 +2002,27 @@
       </c>
       <c r="E26" s="6">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F26" s="6" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G26" s="6">
-        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H26" s="6">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="7">
-        <v>46130</v>
+        <v>46142</v>
       </c>
       <c r="K26" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L26" s="8">
         <v>0.91666666666666663</v>
@@ -2043,10 +2033,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2054,31 +2044,31 @@
       </c>
       <c r="E27" s="6">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F27" s="6" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>KL</v>
       </c>
       <c r="G27" s="6">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" s="7">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="K27" s="8">
         <v>0.79166666666666663</v>
       </c>
       <c r="L27" s="8">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -2086,42 +2076,42 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D28" s="6" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E28" s="6">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F28" s="6" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>KL</v>
       </c>
       <c r="G28" s="6">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J28" s="7">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="K28" s="8">
-        <v>0.47916666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="L28" s="8">
-        <v>0.70833333333333337</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -2129,14 +2119,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D29" s="6" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E29" s="6">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2144,123 +2134,124 @@
       </c>
       <c r="F29" s="6" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G29" s="6">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29" s="6">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="6">
         <v>2</v>
       </c>
       <c r="J29" s="7">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="K29" s="8">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D30" s="6" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E30" s="6">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F30" s="6" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>BL</v>
       </c>
       <c r="G30" s="6">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J30" s="7">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="K30" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L30" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="6" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D31" s="6" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E31" s="6">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F31" s="6" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>BL</v>
       </c>
       <c r="G31" s="6">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J31" s="7">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="K31" s="8">
-        <v>0.6875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L31" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="6" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" s="6" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2268,83 +2259,85 @@
       </c>
       <c r="E32" s="6">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F32" s="6" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G32" s="6">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H32" s="6">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J32" s="7">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="K32" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="L32" s="8">
-        <v>0.83333333333333337</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D33" s="6" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Party</v>
       </c>
       <c r="E33" s="6">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F33" s="6" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G33" s="6">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H33" s="6">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I33" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J33" s="7">
         <v>46137</v>
       </c>
       <c r="K33" s="8">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L33" s="8">
-        <v>0.95833333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D34" s="6" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2352,41 +2345,41 @@
       </c>
       <c r="E34" s="6">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F34" s="6" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G34" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="6">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J34" s="7">
-        <v>46141</v>
+        <v>46138</v>
       </c>
       <c r="K34" s="8">
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L34" s="8">
-        <v>0.91666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2394,41 +2387,42 @@
       </c>
       <c r="E35" s="6">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F35" s="6" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G35" s="6">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H35" s="6">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J35" s="7">
         <v>46142</v>
       </c>
       <c r="K35" s="8">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="L35" s="8">
-        <v>0.91666666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" s="6" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2436,457 +2430,28 @@
       </c>
       <c r="E36" s="6">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F36" s="6" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G36" s="6">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H36" s="6">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" s="7">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="K36" s="8">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="6">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E37" s="6">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
-      </c>
-      <c r="F37" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G37" s="6">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="6">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="6">
-        <v>1</v>
-      </c>
-      <c r="J37" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K37" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="L37" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
-      </c>
-      <c r="E38" s="6">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F38" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G38" s="6">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="6">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I38" s="6">
-        <v>2</v>
-      </c>
-      <c r="J38" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K38" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="6">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E39" s="6">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F39" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G39" s="6">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="6">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="6">
-        <v>1</v>
-      </c>
-      <c r="J39" s="7">
-        <v>46134</v>
-      </c>
-      <c r="K39" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L39" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E40" s="6">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F40" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G40" s="6">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="6">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="6">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7">
-        <v>46141</v>
-      </c>
-      <c r="K40" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L40" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E41" s="6">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
-      </c>
-      <c r="F41" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G41" s="6">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="6">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I41" s="6">
-        <v>1</v>
-      </c>
-      <c r="J41" s="7">
-        <v>46132</v>
-      </c>
-      <c r="K41" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="L41" s="8">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="6">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E42" s="6">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F42" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G42" s="6">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H42" s="6">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I42" s="6">
-        <v>7</v>
-      </c>
-      <c r="J42" s="7">
-        <v>46136</v>
-      </c>
-      <c r="K42" s="8">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L42" s="8">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="6">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Party</v>
-      </c>
-      <c r="E43" s="6">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F43" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G43" s="6">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H43" s="6">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>6</v>
-      </c>
-      <c r="I43" s="6">
-        <v>12</v>
-      </c>
-      <c r="J43" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K43" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L43" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E44" s="6">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F44" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G44" s="6">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I44" s="6">
-        <v>8</v>
-      </c>
-      <c r="J44" s="7">
-        <v>46138</v>
-      </c>
-      <c r="K44" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L44" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E45" s="6">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F45" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G45" s="6">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H45" s="6">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I45" s="6">
-        <v>11</v>
-      </c>
-      <c r="J45" s="7">
-        <v>46142</v>
-      </c>
-      <c r="K45" s="8">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L45" s="8">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="6">
-        <v>46</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E46" s="6">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F46" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G46" s="6">
-        <v>0</v>
-      </c>
-      <c r="H46" s="6">
-        <v>0</v>
-      </c>
-      <c r="I46" s="6">
-        <v>4</v>
-      </c>
-      <c r="J46" s="7">
-        <v>46136</v>
-      </c>
-      <c r="K46" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="L46" s="8">
         <v>0.83333333333333337</v>
       </c>
     </row>
@@ -2900,7 +2465,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C46</xm:sqref>
+          <xm:sqref>C2:C36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2934,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -2989,7 +2554,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -3000,7 +2565,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -3154,7 +2719,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -3176,7 +2741,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -3198,7 +2763,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -3297,7 +2862,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -4940,282 +4505,282 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="str">
-        <f>Events!B19</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B19" s="5">
-        <f>Events!J19</f>
-        <v>46128</v>
+      <c r="A19" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B19" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="str">
-        <f>Events!B20</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B20" s="5">
-        <f>Events!J20</f>
-        <v>46129</v>
+      <c r="A20" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B20" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="str">
-        <f>Events!B21</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B21" s="5">
-        <f>Events!J21</f>
-        <v>46130</v>
+      <c r="A21" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B21" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="str">
-        <f>Events!B22</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B22" s="5">
-        <f>Events!J22</f>
-        <v>46130</v>
+      <c r="A22" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B22" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="str">
-        <f>Events!B23</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B23" s="5">
-        <f>Events!J23</f>
-        <v>46128</v>
+      <c r="A23" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B23" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="str">
-        <f>Events!B24</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B24" s="5">
-        <f>Events!J24</f>
-        <v>46129</v>
+      <c r="A24" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B24" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="str">
-        <f>Events!B25</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B25" s="5">
-        <f>Events!J25</f>
-        <v>46130</v>
+      <c r="A25" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B25" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="str">
-        <f>Events!B26</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B26" s="5">
-        <f>Events!J26</f>
-        <v>46130</v>
+      <c r="A26" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B26" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <f>Events!B27</f>
+        <f>Events!B19</f>
         <v>NB</v>
       </c>
       <c r="B27" s="5">
-        <f>Events!J27</f>
+        <f>Events!J19</f>
         <v>46129</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <f>Events!B28</f>
+        <f>Events!B20</f>
         <v>DWC</v>
       </c>
       <c r="B28" s="5">
-        <f>Events!J28</f>
+        <f>Events!J20</f>
         <v>46130</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <f>Events!B29</f>
+        <f>Events!B21</f>
         <v>SÍ</v>
       </c>
       <c r="B29" s="5">
-        <f>Events!J29</f>
+        <f>Events!J21</f>
         <v>46131</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <f>Events!B30</f>
+        <f>Events!B22</f>
         <v>KP</v>
       </c>
       <c r="B30" s="5">
-        <f>Events!J30</f>
+        <f>Events!J22</f>
         <v>46131</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="str">
-        <f>Events!B31</f>
-        <v>Barna dans</v>
-      </c>
-      <c r="B31" s="5">
-        <f>Events!J31</f>
-        <v>46133</v>
+      <c r="A31" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B31" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>Events!B32</f>
+        <f>Events!B23</f>
         <v>UpT</v>
       </c>
       <c r="B32" s="5">
-        <f>Events!J32</f>
+        <f>Events!J23</f>
         <v>46134</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
+        <f>Events!B24</f>
+        <v>LR</v>
+      </c>
+      <c r="B33" s="5">
+        <f>Events!J24</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>Events!B25</f>
+        <v>FB</v>
+      </c>
+      <c r="B34" s="5">
+        <f>Events!J25</f>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>Events!B26</f>
+        <v>FB</v>
+      </c>
+      <c r="B35" s="5">
+        <f>Events!J26</f>
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>Events!B27</f>
+        <v>SR</v>
+      </c>
+      <c r="B36" s="5">
+        <f>Events!J27</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>Events!B28</f>
+        <v>HT</v>
+      </c>
+      <c r="B37" s="5">
+        <f>Events!J28</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
+        <f>Events!B29</f>
+        <v>K&amp;B</v>
+      </c>
+      <c r="B38" s="5">
+        <f>Events!J29</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f>Events!B30</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B39" s="5">
+        <f>Events!J30</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>Events!B31</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B40" s="5">
+        <f>Events!J31</f>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B41" s="5" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>Events!B32</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B42" s="5">
+        <f>Events!J32</f>
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
         <f>Events!B33</f>
-        <v>LR</v>
-      </c>
-      <c r="B33" s="5">
+        <v>DP</v>
+      </c>
+      <c r="B43" s="5">
         <f>Events!J33</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="str">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
         <f>Events!B34</f>
-        <v>FB</v>
-      </c>
-      <c r="B34" s="5">
+        <v>VR</v>
+      </c>
+      <c r="B44" s="5">
         <f>Events!J34</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="str">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
         <f>Events!B35</f>
-        <v>FB</v>
-      </c>
-      <c r="B35" s="5">
+        <v>Sinfó</v>
+      </c>
+      <c r="B45" s="5">
         <f>Events!J35</f>
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="str">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
         <f>Events!B36</f>
         <v>SR</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B46" s="5">
         <f>Events!J36</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="str">
-        <f>Events!B37</f>
-        <v>HT</v>
-      </c>
-      <c r="B37" s="5">
-        <f>Events!J37</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="str">
-        <f>Events!B38</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B38" s="5">
-        <f>Events!J38</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="str">
-        <f>Events!B39</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B39" s="5">
-        <f>Events!J39</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="str">
-        <f>Events!B40</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B40" s="5">
-        <f>Events!J40</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="str">
-        <f>Events!B41</f>
-        <v>KV</v>
-      </c>
-      <c r="B41" s="5">
-        <f>Events!J41</f>
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="str">
-        <f>Events!B42</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B42" s="5">
-        <f>Events!J42</f>
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="str">
-        <f>Events!B43</f>
-        <v>DP</v>
-      </c>
-      <c r="B43" s="5">
-        <f>Events!J43</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="str">
-        <f>Events!B44</f>
-        <v>VR</v>
-      </c>
-      <c r="B44" s="5">
-        <f>Events!J44</f>
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="str">
-        <f>Events!B45</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B45" s="5">
-        <f>Events!J45</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="str">
-        <f>Events!B46</f>
-        <v>SR</v>
-      </c>
-      <c r="B46" s="5">
-        <f>Events!J46</f>
         <v>46136</v>
       </c>
     </row>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713C1F66-9E66-0741-90E5-35032EA6DFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6366FFE4-3EB1-9B46-A43D-CBCE5EC13309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -2452,7 +2452,7 @@
         <v>0.75</v>
       </c>
       <c r="L36" s="8">
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
     </row>
   </sheetData>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6366FFE4-3EB1-9B46-A43D-CBCE5EC13309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DA1D64-69EF-43B5-A2FA-955EBCC987FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
   <si>
     <t>Event</t>
   </si>
@@ -148,123 +147,9 @@
     <t>EventRanking</t>
   </si>
   <si>
-    <t>Mínus</t>
-  </si>
-  <si>
-    <t>Helgi, kominn með aðra helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 4 helgar</t>
-  </si>
-  <si>
-    <t>Helgi, var með helgi síðast</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 4 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 5 helgar</t>
-  </si>
-  <si>
-    <t>Salur</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Vika</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Hvað hún er löng</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Langar vaktir</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
-  </si>
-  <si>
-    <t>Með hverjum?</t>
-  </si>
-  <si>
     <t>Skillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 2 en þú ert 1</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 en þú ert 3</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 og þú ert</t>
-  </si>
-  <si>
     <t>Upprás</t>
   </si>
   <si>
@@ -322,12 +207,6 @@
     <t>EmpSkillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 1 en þú ert ekki</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
-  </si>
-  <si>
     <t>Req_this_shift</t>
   </si>
   <si>
@@ -451,6 +330,9 @@
     <t>IA</t>
   </si>
   <si>
+    <t>MÍT</t>
+  </si>
+  <si>
     <t>NB</t>
   </si>
   <si>
@@ -463,6 +345,9 @@
     <t>KP</t>
   </si>
   <si>
+    <t>Barna dans</t>
+  </si>
+  <si>
     <t>UpT</t>
   </si>
   <si>
@@ -476,6 +361,9 @@
   </si>
   <si>
     <t>HT</t>
+  </si>
+  <si>
+    <t>KV</t>
   </si>
   <si>
     <t>DP</t>
@@ -562,18 +450,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,18 +792,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -930,7 +814,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -957,1502 +841,1927 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F2" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>1</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="4">
         <v>46113</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="6" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="str">
+      <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F3" s="6" t="str">
+      <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I3" s="6">
-        <v>1</v>
-      </c>
-      <c r="J3" s="7">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4">
         <v>46113</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="5">
         <v>0.6875</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="str">
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I4" s="6">
-        <v>13</v>
-      </c>
-      <c r="J4" s="7">
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4" s="4">
         <v>46113</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="5">
         <v>0.9375</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6" t="str">
+      <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F5" s="6" t="str">
+      <c r="F5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
         <v>46114</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="5">
         <v>0.75</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="6" t="str">
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I6" s="6">
-        <v>12</v>
-      </c>
-      <c r="J6" s="7">
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6" s="4">
         <v>46114</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6" t="str">
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F7" s="6" t="str">
+      <c r="F7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" s="4">
+        <v>46116</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="J7" s="7">
-        <v>46116</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F8" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="4">
         <v>46120</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="6" t="str">
+      <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F9" s="6" t="str">
+      <c r="F9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="4">
         <v>46121</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="5">
         <v>0.75</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="6" t="str">
+      <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F10" s="6" t="str">
+      <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10">
         <v>11</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="4">
         <v>46122</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="5">
         <v>0.75</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="6" t="str">
+      <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F11" s="6" t="str">
+      <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="4">
         <v>46123</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="5">
         <v>0.54166666666666663</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="5">
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="6" t="str">
+      <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>60</v>
       </c>
-      <c r="F12" s="6" t="str">
+      <c r="F12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="6">
-        <v>2</v>
-      </c>
-      <c r="J12" s="7">
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4">
         <v>46123</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="5">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="5">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="str">
+      <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F13" s="6" t="str">
+      <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I13" s="6">
-        <v>1</v>
-      </c>
-      <c r="J13" s="7">
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
         <v>46124</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="5">
         <v>0.54166666666666663</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="5">
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="6" t="str">
+      <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F14" s="6" t="str">
+      <c r="F14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="6">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7">
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
         <v>46124</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="5">
         <v>0.625</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="5">
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="6" t="str">
+      <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F15" s="6" t="str">
+      <c r="F15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I15" s="6">
-        <v>1</v>
-      </c>
-      <c r="J15" s="7">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
         <v>46126</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="6" t="str">
+      <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F16" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>1</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="4">
         <v>46127</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="6" t="str">
+      <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F17" s="6" t="str">
+      <c r="F17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="6">
-        <v>2</v>
-      </c>
-      <c r="J17" s="7">
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17" s="4">
         <v>46127</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="6" t="str">
+      <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F18" s="6" t="str">
+      <c r="F18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="4">
         <v>46128</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="6" t="str">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F19" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G19" s="6">
-        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H19" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>46128</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="7">
-        <v>46129</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6" t="str">
+      <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F20" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G20" s="6">
-        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H20" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I20" s="6">
-        <v>10</v>
-      </c>
-      <c r="J20" s="7">
-        <v>46130</v>
-      </c>
-      <c r="K20" s="8">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="L20" s="8">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
+        <v>46129</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="6" t="str">
+      <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F21" s="6" t="str">
+      <c r="F21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="6">
-        <v>2</v>
-      </c>
-      <c r="J21" s="7">
-        <v>46131</v>
-      </c>
-      <c r="K21" s="8">
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4">
+        <v>46130</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L21" s="5">
         <v>0.625</v>
       </c>
-      <c r="L21" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="6" t="str">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F22" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G22" s="6">
-        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H22" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I22" s="6">
-        <v>12</v>
-      </c>
-      <c r="J22" s="7">
-        <v>46131</v>
-      </c>
-      <c r="K22" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="L22" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="6" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4">
+        <v>46130</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="L22" s="6">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="6" t="str">
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F23" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
+        <v>KL</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <v>1</v>
-      </c>
-      <c r="J23" s="7">
-        <v>46134</v>
-      </c>
-      <c r="K23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4">
+        <v>46128</v>
+      </c>
+      <c r="K23" s="5">
         <v>0.66666666666666663</v>
       </c>
-      <c r="L23" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
+      <c r="L23" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="6" t="str">
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F24" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
+        <v>KL</v>
+      </c>
+      <c r="G24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="6">
-        <v>2</v>
-      </c>
-      <c r="J24" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K24" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L24" s="8">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>46129</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="6" t="str">
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F25" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
+        <v>KL</v>
+      </c>
+      <c r="G25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <v>2</v>
-      </c>
-      <c r="J25" s="7">
-        <v>46141</v>
-      </c>
-      <c r="K25" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L25" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
+        <v>46130</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="6" t="str">
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F26" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6">
+        <v>KL</v>
+      </c>
+      <c r="G26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="6">
-        <v>2</v>
-      </c>
-      <c r="J26" s="7">
-        <v>46142</v>
-      </c>
-      <c r="K26" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
+        <v>46130</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L26" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="6" t="str">
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
-      </c>
-      <c r="F27" s="6" t="str">
+        <v>70</v>
+      </c>
+      <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G27" s="6">
+        <v>EB</v>
+      </c>
+      <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
+        <v>1</v>
+      </c>
+      <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I27" s="6">
-        <v>1</v>
-      </c>
-      <c r="J27" s="7">
-        <v>46134</v>
-      </c>
-      <c r="K27" s="8">
+        <v>4</v>
+      </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
+      <c r="J27" s="4">
+        <v>46129</v>
+      </c>
+      <c r="K27" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L27" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
+      <c r="L27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="6" t="str">
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E28" s="6">
+        <v>Basic</v>
+      </c>
+      <c r="E28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
-      </c>
-      <c r="F28" s="6" t="str">
+        <v>70</v>
+      </c>
+      <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G28" s="6">
+        <v>EB</v>
+      </c>
+      <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
+        <v>1</v>
+      </c>
+      <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="6">
-        <v>1</v>
-      </c>
-      <c r="J28" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K28" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="L28" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28" s="4">
+        <v>46130</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="6" t="str">
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
-      </c>
-      <c r="E29" s="6">
+        <v>Basic</v>
+      </c>
+      <c r="E29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F29" s="6" t="str">
+      <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G29" s="6">
-        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I29" s="6">
-        <v>2</v>
-      </c>
-      <c r="J29" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K29" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="L29" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" s="4">
+        <v>46131</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="6" t="str">
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E30" s="6">
+        <v>Basic</v>
+      </c>
+      <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F30" s="6" t="str">
+        <v>70</v>
+      </c>
+      <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G30" s="6">
+        <v>EB</v>
+      </c>
+      <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="6">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="6">
-        <v>1</v>
-      </c>
-      <c r="J30" s="7">
-        <v>46134</v>
-      </c>
-      <c r="K30" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L30" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6">
+        <v>4</v>
+      </c>
+      <c r="I30">
+        <v>12</v>
+      </c>
+      <c r="J30" s="4">
+        <v>46131</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="6" t="str">
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E31" s="6">
+        <v>Barna</v>
+      </c>
+      <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F31" s="6" t="str">
+        <v>70</v>
+      </c>
+      <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G31" s="6">
+        <v>EB</v>
+      </c>
+      <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
+        <v>1</v>
+      </c>
+      <c r="H31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="6">
-        <v>1</v>
-      </c>
-      <c r="J31" s="7">
-        <v>46141</v>
-      </c>
-      <c r="K31" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L31" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6">
-        <v>31</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31" s="4">
+        <v>46133</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F32" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G32" s="6">
-        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H32" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I32" s="6">
-        <v>7</v>
-      </c>
-      <c r="J32" s="7">
-        <v>46136</v>
-      </c>
-      <c r="K32" s="8">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L32" s="8">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6">
-        <v>32</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4">
+        <v>46134</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Party</v>
-      </c>
-      <c r="E33" s="6">
+        <v>Basic</v>
+      </c>
+      <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F33" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G33" s="6">
-        <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H33" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" t="s">
         <v>6</v>
       </c>
-      <c r="I33" s="6">
-        <v>12</v>
-      </c>
-      <c r="J33" s="7">
-        <v>46137</v>
-      </c>
-      <c r="K33" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L33" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6">
-        <v>33</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="6" t="str">
+      <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F34" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G34" s="6">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I34" s="6">
-        <v>8</v>
-      </c>
-      <c r="J34" s="7">
-        <v>46138</v>
-      </c>
-      <c r="K34" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L34" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="6">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34" s="4">
+        <v>46141</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F35" s="6" t="str">
+        <v>80</v>
+      </c>
+      <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G35" s="6">
-        <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H35" s="6">
+        <v>NL</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35" s="4">
+        <v>46142</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
         <v>3</v>
       </c>
-      <c r="I35" s="6">
-        <v>11</v>
-      </c>
-      <c r="J35" s="7">
-        <v>46142</v>
-      </c>
-      <c r="K35" s="8">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L35" s="8">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="6" t="str">
+      <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>40</v>
+      </c>
+      <c r="F36" t="str">
+        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G36">
+        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4">
+        <v>46134</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="str">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>100</v>
+      </c>
+      <c r="F37" t="str">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="str">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F36" s="6" t="str">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
+      <c r="F38" t="str">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="str">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F39" t="str">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>BL</v>
+      </c>
+      <c r="G39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
+        <v>46134</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="str">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E40">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F40" t="str">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>BL</v>
+      </c>
+      <c r="G40">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" s="4">
+        <v>46141</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" t="str">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>40</v>
+      </c>
+      <c r="F41" t="str">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
+        <v>46132</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="str">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E42">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F42" t="str">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G42">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I42">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4">
+        <v>46136</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Party</v>
+      </c>
+      <c r="E43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>12</v>
+      </c>
+      <c r="J43" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="str">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E44">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F44" t="str">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>4</v>
+      </c>
+      <c r="I44">
+        <v>8</v>
+      </c>
+      <c r="J44" s="4">
+        <v>46138</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="str">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E45">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F45" t="str">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G45">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I45">
+        <v>11</v>
+      </c>
+      <c r="J45" s="4">
+        <v>46142</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L45" s="5">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="str">
+        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E46">
+        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F46" t="str">
+        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G36" s="6">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6">
-        <v>0</v>
-      </c>
-      <c r="I36" s="6">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>4</v>
       </c>
-      <c r="J36" s="7">
+      <c r="J46" s="4">
         <v>46136</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K46" s="5">
         <v>0.75</v>
       </c>
-      <c r="L36" s="8">
-        <v>0.875</v>
+      <c r="L46" s="5">
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -2465,7 +2774,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C36</xm:sqref>
+          <xm:sqref>C2:C46</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2476,470 +2785,470 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2953,15 +3262,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="31" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2">
         <v>46113</v>
@@ -3055,7 +3364,7 @@
       </c>
       <c r="AF1" s="2"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3150,7 +3459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3176,7 +3485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3190,12 +3499,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3224,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3319,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3414,12 +3723,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3430,12 +3739,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3482,17 +3791,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3527,12 +3836,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3555,12 +3864,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3625,12 +3934,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3644,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3739,17 +4048,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3790,7 +4099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3885,12 +4194,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3913,7 +4222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3936,7 +4245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3962,27 +4271,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4077,17 +4386,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4095,17 +4404,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4140,12 +4449,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4154,13 +4463,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4334,464 +4643,464 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <f>Events!J2</f>
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <f>Events!J3</f>
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <f>Events!J4</f>
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <f>Events!J5</f>
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <f>Events!J6</f>
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <f>Events!J7</f>
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <f>Events!J8</f>
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <f>Events!J9</f>
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <f>Events!J10</f>
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <f>Events!J11</f>
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <f>Events!J12</f>
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <f>Events!J13</f>
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <f>Events!J14</f>
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <f>Events!J15</f>
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <f>Events!J16</f>
         <v>46127</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>IA</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <f>Events!J17</f>
         <v>46127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Sinfó</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <f>Events!J18</f>
         <v>46128</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B19" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B20" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B21" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B22" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B23" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B24" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B25" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B26" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="str">
+        <f>Events!B19</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B19" s="4">
+        <f>Events!J19</f>
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="str">
+        <f>Events!B20</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B20" s="4">
+        <f>Events!J20</f>
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="str">
+        <f>Events!B21</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B21" s="4">
+        <f>Events!J21</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="str">
+        <f>Events!B22</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B22" s="4">
+        <f>Events!J22</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="str">
+        <f>Events!B23</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B23" s="4">
+        <f>Events!J23</f>
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="str">
+        <f>Events!B24</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B24" s="4">
+        <f>Events!J24</f>
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="str">
+        <f>Events!B25</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B25" s="4">
+        <f>Events!J25</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="str">
+        <f>Events!B26</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B26" s="4">
+        <f>Events!J26</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
-        <f>Events!B19</f>
+        <f>Events!B27</f>
         <v>NB</v>
       </c>
-      <c r="B27" s="5">
-        <f>Events!J19</f>
+      <c r="B27" s="4">
+        <f>Events!J27</f>
         <v>46129</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
-        <f>Events!B20</f>
+        <f>Events!B28</f>
         <v>DWC</v>
       </c>
-      <c r="B28" s="5">
-        <f>Events!J20</f>
+      <c r="B28" s="4">
+        <f>Events!J28</f>
         <v>46130</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
-        <f>Events!B21</f>
+        <f>Events!B29</f>
         <v>SÍ</v>
       </c>
-      <c r="B29" s="5">
-        <f>Events!J21</f>
+      <c r="B29" s="4">
+        <f>Events!J29</f>
         <v>46131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
-        <f>Events!B22</f>
+        <f>Events!B30</f>
         <v>KP</v>
       </c>
-      <c r="B30" s="5">
-        <f>Events!J22</f>
+      <c r="B30" s="4">
+        <f>Events!J30</f>
         <v>46131</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B31" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="str">
+        <f>Events!B31</f>
+        <v>Barna dans</v>
+      </c>
+      <c r="B31" s="4">
+        <f>Events!J31</f>
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
-        <f>Events!B23</f>
+        <f>Events!B32</f>
         <v>UpT</v>
       </c>
-      <c r="B32" s="5">
-        <f>Events!J23</f>
+      <c r="B32" s="4">
+        <f>Events!J32</f>
         <v>46134</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
-        <f>Events!B24</f>
+        <f>Events!B33</f>
         <v>LR</v>
       </c>
-      <c r="B33" s="5">
-        <f>Events!J24</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="str">
-        <f>Events!B25</f>
-        <v>FB</v>
-      </c>
-      <c r="B34" s="5">
-        <f>Events!J25</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="str">
-        <f>Events!B26</f>
-        <v>FB</v>
-      </c>
-      <c r="B35" s="5">
-        <f>Events!J26</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="str">
-        <f>Events!B27</f>
-        <v>SR</v>
-      </c>
-      <c r="B36" s="5">
-        <f>Events!J27</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="str">
-        <f>Events!B28</f>
-        <v>HT</v>
-      </c>
-      <c r="B37" s="5">
-        <f>Events!J28</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="str">
-        <f>Events!B29</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B38" s="5">
-        <f>Events!J29</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="str">
-        <f>Events!B30</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B39" s="5">
-        <f>Events!J30</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="str">
-        <f>Events!B31</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B40" s="5">
-        <f>Events!J31</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B41" s="5" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="str">
-        <f>Events!B32</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B42" s="5">
-        <f>Events!J32</f>
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="str">
-        <f>Events!B33</f>
-        <v>DP</v>
-      </c>
-      <c r="B43" s="5">
+      <c r="B33" s="4">
         <f>Events!J33</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="str">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="str">
         <f>Events!B34</f>
-        <v>VR</v>
-      </c>
-      <c r="B44" s="5">
+        <v>FB</v>
+      </c>
+      <c r="B34" s="4">
         <f>Events!J34</f>
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="str">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="str">
         <f>Events!B35</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B45" s="5">
+        <v>FB</v>
+      </c>
+      <c r="B35" s="4">
         <f>Events!J35</f>
         <v>46142</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="str">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="str">
         <f>Events!B36</f>
         <v>SR</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B36" s="4">
         <f>Events!J36</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="str">
+        <f>Events!B37</f>
+        <v>HT</v>
+      </c>
+      <c r="B37" s="4">
+        <f>Events!J37</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="str">
+        <f>Events!B38</f>
+        <v>K&amp;B</v>
+      </c>
+      <c r="B38" s="4">
+        <f>Events!J38</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="str">
+        <f>Events!B39</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B39" s="4">
+        <f>Events!J39</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="str">
+        <f>Events!B40</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B40" s="4">
+        <f>Events!J40</f>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="str">
+        <f>Events!B41</f>
+        <v>KV</v>
+      </c>
+      <c r="B41" s="4">
+        <f>Events!J41</f>
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="str">
+        <f>Events!B42</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B42" s="4">
+        <f>Events!J42</f>
         <v>46136</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="5"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="5"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="5"/>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="str">
+        <f>Events!B43</f>
+        <v>DP</v>
+      </c>
+      <c r="B43" s="4">
+        <f>Events!J43</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="str">
+        <f>Events!B44</f>
+        <v>VR</v>
+      </c>
+      <c r="B44" s="4">
+        <f>Events!J44</f>
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="str">
+        <f>Events!B45</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B45" s="4">
+        <f>Events!J45</f>
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="str">
+        <f>Events!B46</f>
+        <v>SR</v>
+      </c>
+      <c r="B46" s="4">
+        <f>Events!J46</f>
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4801,25 +5110,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4828,9 +5137,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4839,9 +5148,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -4850,9 +5159,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -4861,9 +5170,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -4872,9 +5181,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4884,9 +5193,9 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4895,9 +5204,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -4906,9 +5215,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -4917,9 +5226,9 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -4928,9 +5237,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -4939,7 +5248,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -4950,7 +5259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -4961,7 +5270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -4972,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -4983,7 +5292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -4994,7 +5303,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5005,7 +5314,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5016,9 +5325,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5027,9 +5336,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5038,9 +5347,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5049,9 +5358,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5060,9 +5369,9 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5071,9 +5380,9 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5082,9 +5391,9 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5093,9 +5402,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5105,9 +5414,9 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5117,9 +5426,9 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5129,9 +5438,9 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5140,9 +5449,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5151,9 +5460,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5162,9 +5471,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5173,9 +5482,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5184,9 +5493,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5195,9 +5504,9 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5214,25 +5523,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5243,7 +5552,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5254,7 +5563,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5265,7 +5574,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5276,7 +5585,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5287,7 +5596,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5298,7 +5607,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5309,7 +5618,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5320,7 +5629,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5337,499 +5646,186 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>80</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21">
-        <f>+C20*2</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22">
-        <f>+C21*2</f>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23">
-        <f>+C22*2</f>
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24">
-        <f>+C23*2</f>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>90</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>70</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>70</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
@@ -5846,18 +5842,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5869,12 +5865,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -5892,7 +5888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5903,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5915,12 +5911,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -5938,12 +5934,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -5961,12 +5957,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -5984,12 +5980,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -6007,12 +6003,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DA1D64-69EF-43B5-A2FA-955EBCC987FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87955A77-818D-AC47-9275-6E29A7458945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26080" windowHeight="15360" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -793,17 +793,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -841,7 +841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -885,7 +885,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -927,7 +927,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -970,7 +970,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>33</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>35</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>36</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>37</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>38</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>39</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>40</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>41</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>42</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>43</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>44</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>45</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>46</v>
       </c>
@@ -2785,14 +2785,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3262,13 +3262,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF43"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="31" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AF1" s="2"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3499,12 +3499,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3723,12 +3723,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3739,12 +3739,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3791,17 +3791,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3836,12 +3836,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3864,12 +3864,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3934,12 +3934,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4048,17 +4048,89 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4099,7 +4171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4194,12 +4266,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4222,7 +4294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4245,7 +4317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4271,27 +4343,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4386,17 +4458,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4404,17 +4476,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4449,12 +4521,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4463,13 +4535,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ49"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4643,7 +4715,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
@@ -4653,7 +4725,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
@@ -4663,7 +4735,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
@@ -4673,7 +4745,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
@@ -4683,7 +4755,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
@@ -4693,7 +4765,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
@@ -4703,7 +4775,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
@@ -4713,7 +4785,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
@@ -4723,7 +4795,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4733,7 +4805,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4743,7 +4815,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
@@ -4753,7 +4825,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
@@ -4763,7 +4835,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
@@ -4773,7 +4845,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
@@ -4783,7 +4855,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
@@ -4793,7 +4865,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>IA</v>
@@ -4803,7 +4875,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Sinfó</v>
@@ -4813,7 +4885,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MÍT</v>
@@ -4823,7 +4895,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MÍT</v>
@@ -4833,7 +4905,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MÍT</v>
@@ -4843,7 +4915,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>MÍT</v>
@@ -4853,7 +4925,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>MÍT</v>
@@ -4863,7 +4935,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>MÍT</v>
@@ -4873,7 +4945,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>MÍT</v>
@@ -4883,7 +4955,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>MÍT</v>
@@ -4893,7 +4965,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>NB</v>
@@ -4903,7 +4975,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>DWC</v>
@@ -4913,7 +4985,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>SÍ</v>
@@ -4923,7 +4995,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>KP</v>
@@ -4933,7 +5005,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Barna dans</v>
@@ -4943,7 +5015,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>UpT</v>
@@ -4953,7 +5025,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>LR</v>
@@ -4963,7 +5035,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>FB</v>
@@ -4973,7 +5045,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>FB</v>
@@ -4983,7 +5055,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>SR</v>
@@ -4993,7 +5065,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>HT</v>
@@ -5003,7 +5075,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -5013,7 +5085,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Múlinn</v>
@@ -5023,7 +5095,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Múlinn</v>
@@ -5033,7 +5105,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>KV</v>
@@ -5043,7 +5115,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>Sinfó</v>
@@ -5053,7 +5125,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>DP</v>
@@ -5063,7 +5135,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="str">
         <f>Events!B44</f>
         <v>VR</v>
@@ -5073,7 +5145,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
         <f>Events!B45</f>
         <v>Sinfó</v>
@@ -5083,7 +5155,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="str">
         <f>Events!B46</f>
         <v>SR</v>
@@ -5093,13 +5165,13 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
     </row>
   </sheetData>
@@ -5110,12 +5182,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -5126,7 +5198,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -5137,7 +5209,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -5148,7 +5220,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -5159,7 +5231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -5170,7 +5242,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -5181,7 +5253,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -5193,7 +5265,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -5204,7 +5276,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -5215,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -5226,7 +5298,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -5237,7 +5309,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -5248,7 +5320,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5259,7 +5331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5270,7 +5342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5281,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5292,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5303,7 +5375,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5314,7 +5386,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5325,7 +5397,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -5336,7 +5408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -5347,7 +5419,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -5358,7 +5430,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -5369,7 +5441,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -5380,7 +5452,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -5391,7 +5463,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -5402,7 +5474,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -5414,7 +5486,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -5426,7 +5498,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -5438,7 +5510,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -5449,7 +5521,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -5460,7 +5532,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -5471,7 +5543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -5482,7 +5554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -5493,7 +5565,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -5504,7 +5576,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -5523,14 +5595,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -5541,7 +5613,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5552,7 +5624,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5563,7 +5635,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5574,7 +5646,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5585,7 +5657,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5596,7 +5668,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5607,7 +5679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5618,7 +5690,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5629,7 +5701,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5648,17 +5720,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5681,7 +5753,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5704,7 +5776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5727,7 +5799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5750,7 +5822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5773,7 +5845,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5796,7 +5868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5819,7 +5891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5842,7 +5914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5865,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5888,7 +5960,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5911,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5934,7 +6006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5957,7 +6029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5980,7 +6052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6003,7 +6075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87955A77-818D-AC47-9275-6E29A7458945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9996AFF4-7A95-664C-87D4-632228F3A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26080" windowHeight="15360" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="146">
   <si>
     <t>Event</t>
   </si>
@@ -147,9 +148,123 @@
     <t>EventRanking</t>
   </si>
   <si>
+    <t>Mínus</t>
+  </si>
+  <si>
+    <t>Helgi, kominn með aðra helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 4 helgar</t>
+  </si>
+  <si>
+    <t>Helgi, var með helgi síðast</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 4 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 5 helgar</t>
+  </si>
+  <si>
+    <t>Salur</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Vika</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Hvað hún er löng</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Langar vaktir</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
+  </si>
+  <si>
+    <t>Með hverjum?</t>
+  </si>
+  <si>
     <t>Skillset</t>
   </si>
   <si>
+    <t>Ef þarf skillset 2 en þú ert 1</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 3</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert</t>
+  </si>
+  <si>
     <t>Upprás</t>
   </si>
   <si>
@@ -207,6 +322,12 @@
     <t>EmpSkillset</t>
   </si>
   <si>
+    <t>Ef þarf skillset 1 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
+  </si>
+  <si>
     <t>Req_this_shift</t>
   </si>
   <si>
@@ -330,9 +451,6 @@
     <t>IA</t>
   </si>
   <si>
-    <t>MÍT</t>
-  </si>
-  <si>
     <t>NB</t>
   </si>
   <si>
@@ -345,9 +463,6 @@
     <t>KP</t>
   </si>
   <si>
-    <t>Barna dans</t>
-  </si>
-  <si>
     <t>UpT</t>
   </si>
   <si>
@@ -361,9 +476,6 @@
   </si>
   <si>
     <t>HT</t>
-  </si>
-  <si>
-    <t>KV</t>
   </si>
   <si>
     <t>DP</t>
@@ -457,7 +569,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -792,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
@@ -814,7 +928,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -849,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -857,11 +971,11 @@
       </c>
       <c r="E2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>KL</v>
       </c>
       <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -890,7 +1004,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -932,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -958,7 +1072,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4">
         <v>46113</v>
@@ -975,7 +1089,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1017,7 +1131,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -1043,7 +1157,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4">
         <v>46114</v>
@@ -1060,7 +1174,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
@@ -1086,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4">
         <v>46116</v>
@@ -1114,7 +1228,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1277,7 +1391,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1319,7 +1433,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -1404,7 +1518,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -1458,7 +1572,7 @@
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1491,7 +1605,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -1517,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4">
         <v>46127</v>
@@ -1578,10 +1692,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1589,30 +1703,31 @@
       </c>
       <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="K19" s="5">
-        <v>0.6875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L19" s="5">
-        <v>0.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -1620,10 +1735,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1631,30 +1746,31 @@
       </c>
       <c r="E20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="K20" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L20" s="5">
-        <v>0.875</v>
+        <v>0.70833333333333337</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -1662,7 +1778,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -1687,27 +1803,27 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="K21" s="5">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="L21" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1715,41 +1831,42 @@
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="K22" s="5">
-        <v>0.625</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1757,30 +1874,30 @@
       </c>
       <c r="E23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" s="4">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="K23" s="5">
         <v>0.66666666666666663</v>
       </c>
       <c r="L23" s="5">
-        <v>0.91666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -1788,10 +1905,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1799,31 +1916,30 @@
       </c>
       <c r="E24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G24">
-        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4">
-        <v>46129</v>
+        <v>46137</v>
       </c>
       <c r="K24" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L24" s="5">
-        <v>0.91666666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -1831,10 +1947,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1842,31 +1958,30 @@
       </c>
       <c r="E25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G25">
-        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="4">
-        <v>46130</v>
+        <v>46141</v>
       </c>
       <c r="K25" s="5">
-        <v>0.41666666666666669</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L25" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1874,10 +1989,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1885,28 +2000,27 @@
       </c>
       <c r="E26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G26">
-        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="4">
-        <v>46130</v>
+        <v>46142</v>
       </c>
       <c r="K26" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L26" s="5">
         <v>0.91666666666666663</v>
@@ -1917,10 +2031,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1928,31 +2042,31 @@
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>KL</v>
       </c>
       <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="K27" s="5">
         <v>0.79166666666666663</v>
       </c>
       <c r="L27" s="5">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -1960,42 +2074,42 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>KL</v>
       </c>
       <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="K28" s="5">
-        <v>0.47916666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="L28" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -2003,14 +2117,14 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2018,123 +2132,124 @@
       </c>
       <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="K29" s="5">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>BL</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="K30" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L30" s="5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>BL</v>
       </c>
       <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="K31" s="5">
-        <v>0.6875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L31" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2142,83 +2257,85 @@
       </c>
       <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="K32" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="L32" s="5">
-        <v>0.83333333333333337</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Party</v>
       </c>
       <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4">
         <v>46137</v>
       </c>
       <c r="K33" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L33" s="5">
-        <v>0.95833333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2226,41 +2343,41 @@
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4">
-        <v>46141</v>
+        <v>46138</v>
       </c>
       <c r="K34" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L34" s="5">
-        <v>0.91666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2268,41 +2385,42 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4">
         <v>46142</v>
       </c>
       <c r="K35" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="L35" s="5">
-        <v>0.91666666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2310,458 +2428,29 @@
       </c>
       <c r="E36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G36">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H36">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" s="4">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="K36" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" t="str">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
-      </c>
-      <c r="F37" t="str">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37" s="4">
-        <v>46137</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L37" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" t="str">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
-      </c>
-      <c r="E38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F38" t="str">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I38">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4">
-        <v>46137</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" t="str">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F39" t="str">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39" s="4">
-        <v>46134</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L39" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>40</v>
-      </c>
-      <c r="B40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" t="str">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E40">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F40" t="str">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G40">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40" s="4">
-        <v>46141</v>
-      </c>
-      <c r="K40" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L40" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" t="str">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
-      </c>
-      <c r="F41" t="str">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4">
-        <v>46132</v>
-      </c>
-      <c r="K41" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L41" s="5">
         <v>0.875</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>42</v>
-      </c>
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" t="str">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E42">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F42" t="str">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G42">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I42">
-        <v>7</v>
-      </c>
-      <c r="J42" s="4">
-        <v>46136</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L42" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Party</v>
-      </c>
-      <c r="E43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>6</v>
-      </c>
-      <c r="I43">
-        <v>12</v>
-      </c>
-      <c r="J43" s="4">
-        <v>46137</v>
-      </c>
-      <c r="K43" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L43" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>44</v>
-      </c>
-      <c r="B44" t="s">
-        <v>101</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" t="str">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E44">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F44" t="str">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I44">
-        <v>8</v>
-      </c>
-      <c r="J44" s="4">
-        <v>46138</v>
-      </c>
-      <c r="K44" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L44" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>45</v>
-      </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" t="str">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E45">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
-      </c>
-      <c r="F45" t="str">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G45">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I45">
-        <v>11</v>
-      </c>
-      <c r="J45" s="4">
-        <v>46142</v>
-      </c>
-      <c r="K45" s="5">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L45" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" t="str">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E46">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F46" t="str">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>4</v>
-      </c>
-      <c r="J46" s="4">
-        <v>46136</v>
-      </c>
-      <c r="K46" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L46" s="5">
-        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -2774,7 +2463,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C46</xm:sqref>
+          <xm:sqref>C2:C36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2794,13 +2483,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2808,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -2819,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2830,7 +2519,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -2841,7 +2530,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -2852,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2863,7 +2552,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2874,7 +2563,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2885,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2896,7 +2585,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2907,7 +2596,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2918,7 +2607,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2929,7 +2618,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -2940,7 +2629,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2951,7 +2640,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2962,7 +2651,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -2973,7 +2662,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2984,7 +2673,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2995,7 +2684,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -3006,7 +2695,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -3017,7 +2706,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -3028,7 +2717,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -3039,7 +2728,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -3050,7 +2739,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -3061,7 +2750,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -3072,7 +2761,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -3083,7 +2772,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -3094,7 +2783,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -3105,7 +2794,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -3116,7 +2805,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -3127,7 +2816,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3138,7 +2827,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -3149,7 +2838,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -3160,7 +2849,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -3171,7 +2860,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -3182,7 +2871,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -3193,7 +2882,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -3204,7 +2893,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -3215,7 +2904,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3226,7 +2915,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -3237,7 +2926,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -3248,7 +2937,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3261,16 +2950,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2">
         <v>46113</v>
@@ -3363,8 +3053,9 @@
         <v>46142</v>
       </c>
       <c r="AF1" s="2"/>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH1" s="2"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3458,8 +3149,23 @@
       <c r="AE2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <f>COUNT(B2:AE2)</f>
+        <v>30</v>
+      </c>
+      <c r="AH2">
+        <f>$AK$2-AG2</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f>AH2/$AK$2</f>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3484,8 +3190,20 @@
       <c r="U3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AG45" si="0">COUNT(B3:AE3)</f>
+        <v>7</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" ref="AH3:AH42" si="1">$AK$2-AG3</f>
+        <v>23</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI42" si="2">AH3/$AK$2</f>
+        <v>0.76666666666666672</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3498,13 +3216,37 @@
       <c r="V4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3532,8 +3274,20 @@
       <c r="M6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>0.73333333333333328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3627,8 +3381,20 @@
       <c r="AE7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3722,13 +3488,37 @@
       <c r="AE8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3738,13 +3528,37 @@
       <c r="V10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="2"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3790,18 +3604,54 @@
       <c r="V12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="2"/>
+        <v>0.53333333333333333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3835,13 +3685,37 @@
       <c r="Q15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="2"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3863,13 +3737,37 @@
       <c r="G17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3933,13 +3831,37 @@
       <c r="U19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG19">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3952,8 +3874,20 @@
       <c r="V21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4047,90 +3981,54 @@
       <c r="AE22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG22">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI23">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AB24">
-        <v>1</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AD24">
-        <v>1</v>
-      </c>
-      <c r="AE24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4170,8 +4068,20 @@
       <c r="V25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG25">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4265,13 +4175,37 @@
       <c r="AE26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG26">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI27">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4293,8 +4227,20 @@
       <c r="G28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG28">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="AI28">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4316,8 +4262,20 @@
       <c r="I29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG29">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4342,28 +4300,88 @@
       <c r="I30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG30">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="AI30">
+        <f t="shared" si="2"/>
+        <v>0.76666666666666672</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4457,36 +4475,108 @@
       <c r="AE35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG35">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AH35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI36">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG38">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH38">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AI38">
+        <f t="shared" si="2"/>
+        <v>0.96666666666666667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI39">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4520,13 +4610,37 @@
       <c r="V41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AH41">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="AI41">
+        <f t="shared" si="2"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="AG42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH42">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI42">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4886,282 +5000,282 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="str">
-        <f>Events!B19</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B19" s="4">
-        <f>Events!J19</f>
-        <v>46128</v>
+      <c r="A19" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B19" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="str">
-        <f>Events!B20</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B20" s="4">
-        <f>Events!J20</f>
-        <v>46129</v>
+      <c r="A20" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B20" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="str">
-        <f>Events!B21</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B21" s="4">
-        <f>Events!J21</f>
-        <v>46130</v>
+      <c r="A21" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B21" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="str">
-        <f>Events!B22</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B22" s="4">
-        <f>Events!J22</f>
-        <v>46130</v>
+      <c r="A22" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B22" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="str">
-        <f>Events!B23</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B23" s="4">
-        <f>Events!J23</f>
-        <v>46128</v>
+      <c r="A23" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B23" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="str">
-        <f>Events!B24</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B24" s="4">
-        <f>Events!J24</f>
-        <v>46129</v>
+      <c r="A24" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B24" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="str">
-        <f>Events!B25</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B25" s="4">
-        <f>Events!J25</f>
-        <v>46130</v>
+      <c r="A25" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B25" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="str">
-        <f>Events!B26</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B26" s="4">
-        <f>Events!J26</f>
-        <v>46130</v>
+      <c r="A26" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B26" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <f>Events!B27</f>
+        <f>Events!B19</f>
         <v>NB</v>
       </c>
       <c r="B27" s="4">
-        <f>Events!J27</f>
+        <f>Events!J19</f>
         <v>46129</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <f>Events!B28</f>
+        <f>Events!B20</f>
         <v>DWC</v>
       </c>
       <c r="B28" s="4">
-        <f>Events!J28</f>
+        <f>Events!J20</f>
         <v>46130</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <f>Events!B29</f>
+        <f>Events!B21</f>
         <v>SÍ</v>
       </c>
       <c r="B29" s="4">
-        <f>Events!J29</f>
+        <f>Events!J21</f>
         <v>46131</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <f>Events!B30</f>
+        <f>Events!B22</f>
         <v>KP</v>
       </c>
       <c r="B30" s="4">
-        <f>Events!J30</f>
+        <f>Events!J22</f>
         <v>46131</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="str">
-        <f>Events!B31</f>
-        <v>Barna dans</v>
-      </c>
-      <c r="B31" s="4">
-        <f>Events!J31</f>
-        <v>46133</v>
+      <c r="A31" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B31" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>Events!B32</f>
+        <f>Events!B23</f>
         <v>UpT</v>
       </c>
       <c r="B32" s="4">
-        <f>Events!J32</f>
+        <f>Events!J23</f>
         <v>46134</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
+        <f>Events!B24</f>
+        <v>LR</v>
+      </c>
+      <c r="B33" s="4">
+        <f>Events!J24</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>Events!B25</f>
+        <v>FB</v>
+      </c>
+      <c r="B34" s="4">
+        <f>Events!J25</f>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>Events!B26</f>
+        <v>FB</v>
+      </c>
+      <c r="B35" s="4">
+        <f>Events!J26</f>
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>Events!B27</f>
+        <v>SR</v>
+      </c>
+      <c r="B36" s="4">
+        <f>Events!J27</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>Events!B28</f>
+        <v>HT</v>
+      </c>
+      <c r="B37" s="4">
+        <f>Events!J28</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
+        <f>Events!B29</f>
+        <v>K&amp;B</v>
+      </c>
+      <c r="B38" s="4">
+        <f>Events!J29</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f>Events!B30</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B39" s="4">
+        <f>Events!J30</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>Events!B31</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B40" s="4">
+        <f>Events!J31</f>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B41" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>Events!B32</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B42" s="4">
+        <f>Events!J32</f>
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
         <f>Events!B33</f>
-        <v>LR</v>
-      </c>
-      <c r="B33" s="4">
+        <v>DP</v>
+      </c>
+      <c r="B43" s="4">
         <f>Events!J33</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="str">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
         <f>Events!B34</f>
-        <v>FB</v>
-      </c>
-      <c r="B34" s="4">
+        <v>VR</v>
+      </c>
+      <c r="B44" s="4">
         <f>Events!J34</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="str">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
         <f>Events!B35</f>
-        <v>FB</v>
-      </c>
-      <c r="B35" s="4">
+        <v>Sinfó</v>
+      </c>
+      <c r="B45" s="4">
         <f>Events!J35</f>
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="str">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
         <f>Events!B36</f>
         <v>SR</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B46" s="4">
         <f>Events!J36</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="str">
-        <f>Events!B37</f>
-        <v>HT</v>
-      </c>
-      <c r="B37" s="4">
-        <f>Events!J37</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="str">
-        <f>Events!B38</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B38" s="4">
-        <f>Events!J38</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="str">
-        <f>Events!B39</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B39" s="4">
-        <f>Events!J39</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="str">
-        <f>Events!B40</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B40" s="4">
-        <f>Events!J40</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="str">
-        <f>Events!B41</f>
-        <v>KV</v>
-      </c>
-      <c r="B41" s="4">
-        <f>Events!J41</f>
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="str">
-        <f>Events!B42</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B42" s="4">
-        <f>Events!J42</f>
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="str">
-        <f>Events!B43</f>
-        <v>DP</v>
-      </c>
-      <c r="B43" s="4">
-        <f>Events!J43</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="str">
-        <f>Events!B44</f>
-        <v>VR</v>
-      </c>
-      <c r="B44" s="4">
-        <f>Events!J44</f>
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="str">
-        <f>Events!B45</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B45" s="4">
-        <f>Events!J45</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="str">
-        <f>Events!B46</f>
-        <v>SR</v>
-      </c>
-      <c r="B46" s="4">
-        <f>Events!J46</f>
         <v>46136</v>
       </c>
     </row>
@@ -5189,18 +5303,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5211,7 +5325,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -5222,7 +5336,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -5233,7 +5347,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -5244,7 +5358,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -5255,7 +5369,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5267,7 +5381,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5278,7 +5392,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -5289,7 +5403,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -5300,7 +5414,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -5311,7 +5425,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -5399,7 +5513,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5410,7 +5524,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5421,7 +5535,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5432,7 +5546,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5443,7 +5557,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5454,7 +5568,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5465,7 +5579,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5476,7 +5590,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5488,7 +5602,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5500,7 +5614,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5512,7 +5626,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5523,7 +5637,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5534,7 +5648,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5545,7 +5659,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5556,7 +5670,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5567,7 +5681,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5578,7 +5692,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5604,13 +5718,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -5718,6 +5832,319 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21">
+        <f>+C20*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <f>+C21*2</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <f>+C22*2</f>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <f>+C23*2</f>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5735,7 +6162,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5758,13 +6185,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5781,7 +6208,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -5804,7 +6231,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -5827,7 +6254,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -5850,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -5873,7 +6300,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -5896,7 +6323,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -5919,13 +6346,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5942,7 +6369,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -5971,7 +6398,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5988,7 +6415,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -6011,7 +6438,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -6034,7 +6461,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -6057,7 +6484,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -6080,7 +6507,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9996AFF4-7A95-664C-87D4-632228F3A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E02926-D67B-4549-9444-F0426FAD807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -907,17 +907,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -955,7 +955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -999,7 +999,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2474,14 +2474,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2951,14 +2951,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AK43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="31" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="AF1" s="2"/>
       <c r="AH1" s="2"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="AG3">
-        <f t="shared" ref="AG3:AG45" si="0">COUNT(B3:AE3)</f>
+        <f t="shared" ref="AG3:AG42" si="0">COUNT(B3:AE3)</f>
         <v>7</v>
       </c>
       <c r="AH3">
@@ -3203,7 +3203,7 @@
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4649,13 +4649,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4829,7 +4829,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
@@ -4839,7 +4839,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
@@ -4849,7 +4849,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
@@ -4859,7 +4859,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
@@ -4869,7 +4869,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
@@ -4879,7 +4879,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
@@ -4889,7 +4889,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
@@ -4899,7 +4899,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
@@ -4909,7 +4909,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4919,7 +4919,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4929,7 +4929,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
@@ -4939,7 +4939,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
@@ -4949,7 +4949,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
@@ -4959,7 +4959,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
@@ -4969,7 +4969,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
@@ -4979,7 +4979,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>IA</v>
@@ -4989,7 +4989,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Sinfó</v>
@@ -4999,7 +4999,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5009,7 +5009,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5019,7 +5019,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5029,7 +5029,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5039,7 +5039,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5049,7 +5049,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5059,7 +5059,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5069,7 +5069,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5079,7 +5079,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B19</f>
         <v>NB</v>
@@ -5089,7 +5089,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B20</f>
         <v>DWC</v>
@@ -5099,7 +5099,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B21</f>
         <v>SÍ</v>
@@ -5109,7 +5109,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B22</f>
         <v>KP</v>
@@ -5119,7 +5119,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5129,7 +5129,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>Events!B23</f>
         <v>UpT</v>
@@ -5139,7 +5139,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>Events!B24</f>
         <v>LR</v>
@@ -5149,7 +5149,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>Events!B25</f>
         <v>FB</v>
@@ -5159,7 +5159,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>Events!B26</f>
         <v>FB</v>
@@ -5169,7 +5169,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>Events!B27</f>
         <v>SR</v>
@@ -5179,7 +5179,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>Events!B28</f>
         <v>HT</v>
@@ -5189,7 +5189,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>Events!B29</f>
         <v>K&amp;B</v>
@@ -5199,7 +5199,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>Events!B30</f>
         <v>Múlinn</v>
@@ -5209,7 +5209,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -5219,7 +5219,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -5229,7 +5229,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>Events!B32</f>
         <v>Sinfó</v>
@@ -5239,7 +5239,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>Events!B33</f>
         <v>DP</v>
@@ -5249,7 +5249,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="str">
         <f>Events!B34</f>
         <v>VR</v>
@@ -5259,7 +5259,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>Events!B35</f>
         <v>Sinfó</v>
@@ -5269,7 +5269,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>Events!B36</f>
         <v>SR</v>
@@ -5279,13 +5279,13 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="4"/>
     </row>
   </sheetData>
@@ -5296,12 +5296,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>78</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>81</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>81</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -5654,10 +5654,10 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>88</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>88</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -5709,14 +5709,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5735,10 +5735,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5746,10 +5746,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5834,20 +5834,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>32</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>37</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>42</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>43</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>44</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>45</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>48</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>49</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>50</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>51</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>54</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>55</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>56</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -6072,12 +6072,12 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>62</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>61</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>65</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>64</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>63</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>86</v>
       </c>
@@ -6147,17 +6147,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -6479,7 +6479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E02926-D67B-4549-9444-F0426FAD807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FE0954-795F-C745-AD58-8DE50FC0395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26080" windowHeight="15360" firstSheet="1" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
   <si>
     <t>Event</t>
   </si>
@@ -148,123 +147,9 @@
     <t>EventRanking</t>
   </si>
   <si>
-    <t>Mínus</t>
-  </si>
-  <si>
-    <t>Helgi, kominn með aðra helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 4 helgar</t>
-  </si>
-  <si>
-    <t>Helgi, var með helgi síðast</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 4 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 5 helgar</t>
-  </si>
-  <si>
-    <t>Salur</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Vika</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Hvað hún er löng</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Langar vaktir</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
-  </si>
-  <si>
-    <t>Með hverjum?</t>
-  </si>
-  <si>
     <t>Skillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 2 en þú ert 1</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 en þú ert 3</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 og þú ert</t>
-  </si>
-  <si>
     <t>Upprás</t>
   </si>
   <si>
@@ -322,12 +207,6 @@
     <t>EmpSkillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 1 en þú ert ekki</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
-  </si>
-  <si>
     <t>Req_this_shift</t>
   </si>
   <si>
@@ -451,6 +330,9 @@
     <t>IA</t>
   </si>
   <si>
+    <t>MÍT</t>
+  </si>
+  <si>
     <t>NB</t>
   </si>
   <si>
@@ -463,6 +345,9 @@
     <t>KP</t>
   </si>
   <si>
+    <t>Barna dans</t>
+  </si>
+  <si>
     <t>UpT</t>
   </si>
   <si>
@@ -476,6 +361,9 @@
   </si>
   <si>
     <t>HT</t>
+  </si>
+  <si>
+    <t>KV</t>
   </si>
   <si>
     <t>DP</t>
@@ -569,9 +457,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,18 +792,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -928,7 +814,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -955,7 +841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -963,7 +849,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -971,11 +857,11 @@
       </c>
       <c r="E2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>BL</v>
       </c>
       <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -999,12 +885,12 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1026,7 +912,7 @@
       </c>
       <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1041,12 +927,12 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -1072,7 +958,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4">
         <v>46113</v>
@@ -1084,12 +970,12 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1111,7 +997,7 @@
       </c>
       <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1126,12 +1012,12 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -1157,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4">
         <v>46114</v>
@@ -1169,12 +1055,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
@@ -1200,7 +1086,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4">
         <v>46116</v>
@@ -1212,7 +1098,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1228,7 +1114,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1256,7 +1142,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1272,7 +1158,7 @@
       </c>
       <c r="E9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1300,7 +1186,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1316,7 +1202,7 @@
       </c>
       <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1343,7 +1229,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1359,7 +1245,7 @@
       </c>
       <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1386,12 +1272,12 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1402,7 +1288,7 @@
       </c>
       <c r="E12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1428,12 +1314,12 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -1444,7 +1330,7 @@
       </c>
       <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1471,7 +1357,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1498,7 +1384,7 @@
       </c>
       <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -1513,12 +1399,12 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -1529,7 +1415,7 @@
       </c>
       <c r="E15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1556,7 +1442,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1572,7 +1458,7 @@
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1600,12 +1486,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -1624,14 +1510,14 @@
       </c>
       <c r="G17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4">
         <v>46127</v>
@@ -1643,7 +1529,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1659,7 +1545,7 @@
       </c>
       <c r="E18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1687,15 +1573,15 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1703,42 +1589,41 @@
       </c>
       <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G19">
-        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4">
-        <v>46129</v>
+        <v>46128</v>
       </c>
       <c r="K19" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="L19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1746,39 +1631,38 @@
       </c>
       <c r="E20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G20">
-        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4">
-        <v>46130</v>
+        <v>46129</v>
       </c>
       <c r="K20" s="5">
-        <v>0.47916666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L20" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -1800,30 +1684,30 @@
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4">
-        <v>46131</v>
+        <v>46130</v>
       </c>
       <c r="K21" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L21" s="5">
         <v>0.625</v>
       </c>
-      <c r="L21" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1831,42 +1715,41 @@
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G22">
-        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4">
-        <v>46131</v>
+        <v>46130</v>
       </c>
       <c r="K22" s="5">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="L22" s="5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.625</v>
+      </c>
+      <c r="L22" s="6">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1878,37 +1761,37 @@
       </c>
       <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" s="4">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="K23" s="5">
         <v>0.66666666666666663</v>
       </c>
       <c r="L23" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1920,37 +1803,38 @@
       </c>
       <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4">
-        <v>46137</v>
+        <v>46129</v>
       </c>
       <c r="K24" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L24" s="5">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1962,37 +1846,38 @@
       </c>
       <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="4">
-        <v>46141</v>
+        <v>46130</v>
       </c>
       <c r="K25" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="L25" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2004,37 +1889,38 @@
       </c>
       <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>46142</v>
+        <v>46130</v>
       </c>
       <c r="K26" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L26" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2042,89 +1928,89 @@
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>EB</v>
       </c>
       <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J27" s="4">
-        <v>46134</v>
+        <v>46129</v>
       </c>
       <c r="K27" s="5">
         <v>0.79166666666666663</v>
       </c>
       <c r="L27" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>EB</v>
       </c>
       <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J28" s="4">
-        <v>46137</v>
+        <v>46130</v>
       </c>
       <c r="K28" s="5">
-        <v>0.75</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L28" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Basic</v>
       </c>
       <c r="E29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2132,10 +2018,9 @@
       </c>
       <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G29">
-        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
@@ -2146,110 +2031,110 @@
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46137</v>
+        <v>46131</v>
       </c>
       <c r="K29" s="5">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="L29" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>EB</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4">
-        <v>46134</v>
+        <v>46131</v>
       </c>
       <c r="K30" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="L30" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Barna</v>
       </c>
       <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>EB</v>
       </c>
       <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J31" s="4">
-        <v>46141</v>
+        <v>46133</v>
       </c>
       <c r="K31" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="L31" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2257,85 +2142,83 @@
       </c>
       <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G32">
-        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="K32" s="5">
-        <v>0.77083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L32" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Party</v>
+        <v>Basic</v>
       </c>
       <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G33">
-        <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J33" s="4">
         <v>46137</v>
       </c>
       <c r="K33" s="5">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L33" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2343,41 +2226,41 @@
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J34" s="4">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="K34" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L34" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2385,42 +2268,41 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>NL</v>
       </c>
       <c r="G35">
-        <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4">
         <v>46142</v>
       </c>
       <c r="K35" s="5">
-        <v>0.77083333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L35" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2432,25 +2314,454 @@
       </c>
       <c r="F36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G36">
+        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4">
+        <v>46134</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="str">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>100</v>
+      </c>
+      <c r="F37" t="str">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="str">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F38" t="str">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="str">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F39" t="str">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>BL</v>
+      </c>
+      <c r="G39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
+        <v>46134</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="str">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E40">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F40" t="str">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>BL</v>
+      </c>
+      <c r="G40">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" s="4">
+        <v>46141</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" t="str">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F41" t="str">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="G41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
+        <v>46132</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="str">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E42">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F42" t="str">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G42">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I42">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4">
+        <v>46136</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Party</v>
+      </c>
+      <c r="E43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>60</v>
+      </c>
+      <c r="F43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>12</v>
+      </c>
+      <c r="J43" s="4">
+        <v>46137</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="str">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E44">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F44" t="str">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>4</v>
+      </c>
+      <c r="I44">
+        <v>8</v>
+      </c>
+      <c r="J44" s="4">
+        <v>46138</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="str">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E45">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F45" t="str">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="G45">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I45">
+        <v>11</v>
+      </c>
+      <c r="J45" s="4">
+        <v>46142</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L45" s="5">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="str">
+        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E46">
+        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F46" t="str">
+        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>4</v>
       </c>
-      <c r="J36" s="4">
+      <c r="J46" s="4">
         <v>46136</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K46" s="5">
         <v>0.75</v>
       </c>
-      <c r="L36" s="5">
-        <v>0.875</v>
+      <c r="L46" s="5">
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -2463,7 +2774,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C36</xm:sqref>
+          <xm:sqref>C2:C46</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2474,470 +2785,470 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2950,17 +3261,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
-  <dimension ref="A1:AK43"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="31" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2">
         <v>46113</v>
@@ -3053,9 +3363,8 @@
         <v>46142</v>
       </c>
       <c r="AF1" s="2"/>
-      <c r="AH1" s="2"/>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3149,23 +3458,8 @@
       <c r="AE2">
         <v>1</v>
       </c>
-      <c r="AG2">
-        <f>COUNT(B2:AE2)</f>
-        <v>30</v>
-      </c>
-      <c r="AH2">
-        <f>$AK$2-AG2</f>
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <f>AH2/$AK$2</f>
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3190,20 +3484,8 @@
       <c r="U3">
         <v>1</v>
       </c>
-      <c r="AG3">
-        <f t="shared" ref="AG3:AG42" si="0">COUNT(B3:AE3)</f>
-        <v>7</v>
-      </c>
-      <c r="AH3">
-        <f t="shared" ref="AH3:AH42" si="1">$AK$2-AG3</f>
-        <v>23</v>
-      </c>
-      <c r="AI3">
-        <f t="shared" ref="AI3:AI42" si="2">AH3/$AK$2</f>
-        <v>0.76666666666666672</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3216,37 +3498,13 @@
       <c r="V4">
         <v>1</v>
       </c>
-      <c r="AG4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH4">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="AI4">
-        <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="AG5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3274,20 +3532,8 @@
       <c r="M6">
         <v>1</v>
       </c>
-      <c r="AG6">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AH6">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="AI6">
-        <f t="shared" si="2"/>
-        <v>0.73333333333333328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3381,20 +3627,8 @@
       <c r="AE7">
         <v>1</v>
       </c>
-      <c r="AG7">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AH7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3488,37 +3722,13 @@
       <c r="AE8">
         <v>1</v>
       </c>
-      <c r="AG8">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AH8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="AG9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3528,37 +3738,13 @@
       <c r="V10">
         <v>1</v>
       </c>
-      <c r="AG10">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="AH10">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="AI10">
-        <f t="shared" si="2"/>
-        <v>0.93333333333333335</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="AG11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI11">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3604,54 +3790,18 @@
       <c r="V12">
         <v>1</v>
       </c>
-      <c r="AG12">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AH12">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AI12">
-        <f t="shared" si="2"/>
-        <v>0.53333333333333333</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="AG13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="AG14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3685,37 +3835,13 @@
       <c r="Q15">
         <v>1</v>
       </c>
-      <c r="AG15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="AG16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI16">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3737,37 +3863,13 @@
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="AG17">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AH17">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="AI17">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="AG18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH18">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI18">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3831,37 +3933,13 @@
       <c r="U19">
         <v>1</v>
       </c>
-      <c r="AG19">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="AH19">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="AI19">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="AG20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI20">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3874,20 +3952,8 @@
       <c r="V21">
         <v>1</v>
       </c>
-      <c r="AG21">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH21">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="AI21">
-        <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3981,54 +4047,90 @@
       <c r="AE22">
         <v>1</v>
       </c>
-      <c r="AG22">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AH22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="AG23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI23">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="AG24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI24">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4068,20 +4170,8 @@
       <c r="V25">
         <v>1</v>
       </c>
-      <c r="AG25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="AH25">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="AI25">
-        <f t="shared" si="2"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4175,37 +4265,13 @@
       <c r="AE26">
         <v>1</v>
       </c>
-      <c r="AG26">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AH26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="AG27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH27">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI27">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4227,20 +4293,8 @@
       <c r="G28">
         <v>1</v>
       </c>
-      <c r="AG28">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AH28">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="AI28">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4262,20 +4316,8 @@
       <c r="I29">
         <v>1</v>
       </c>
-      <c r="AG29">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AH29">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="AI29">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4300,88 +4342,28 @@
       <c r="I30">
         <v>1</v>
       </c>
-      <c r="AG30">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AH30">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="AI30">
-        <f t="shared" si="2"/>
-        <v>0.76666666666666672</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="AG31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH31">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI31">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="AG32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI32">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="AG33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI33">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="AG34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI34">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4475,108 +4457,36 @@
       <c r="AE35">
         <v>1</v>
       </c>
-      <c r="AG35">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AH35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="AG36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH36">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI36">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="AG37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH37">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI37">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="AG38">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH38">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="AI38">
-        <f t="shared" si="2"/>
-        <v>0.96666666666666667</v>
-      </c>
-    </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="AG39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH39">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI39">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="AG40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH40">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI40">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4610,37 +4520,13 @@
       <c r="V41">
         <v>1</v>
       </c>
-      <c r="AG41">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AH41">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="AI41">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="AG42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH42">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="AI42">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:35" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    </row>
+    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4649,13 +4535,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ49"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4829,7 +4715,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
@@ -4839,7 +4725,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
@@ -4849,7 +4735,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
@@ -4859,7 +4745,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
@@ -4869,7 +4755,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
@@ -4879,7 +4765,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
@@ -4889,7 +4775,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
@@ -4899,7 +4785,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
@@ -4909,7 +4795,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4919,7 +4805,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4929,7 +4815,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
@@ -4939,7 +4825,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
@@ -4949,7 +4835,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
@@ -4959,7 +4845,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
@@ -4969,7 +4855,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
@@ -4979,7 +4865,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>IA</v>
@@ -4989,7 +4875,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Sinfó</v>
@@ -4999,293 +4885,293 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B19" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B20" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B21" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B22" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B23" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B24" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B25" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B26" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
+        <f>Events!B19</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B19" s="4">
+        <f>Events!J19</f>
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
+        <f>Events!B20</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B20" s="4">
+        <f>Events!J20</f>
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
+        <f>Events!B21</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B21" s="4">
+        <f>Events!J21</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>Events!B22</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B22" s="4">
+        <f>Events!J22</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
+        <f>Events!B23</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B23" s="4">
+        <f>Events!J23</f>
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
+        <f>Events!B24</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B24" s="4">
+        <f>Events!J24</f>
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
+        <f>Events!B25</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B25" s="4">
+        <f>Events!J25</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
+        <f>Events!B26</f>
+        <v>MÍT</v>
+      </c>
+      <c r="B26" s="4">
+        <f>Events!J26</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <f>Events!B19</f>
+        <f>Events!B27</f>
         <v>NB</v>
       </c>
       <c r="B27" s="4">
-        <f>Events!J19</f>
+        <f>Events!J27</f>
         <v>46129</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <f>Events!B20</f>
+        <f>Events!B28</f>
         <v>DWC</v>
       </c>
       <c r="B28" s="4">
-        <f>Events!J20</f>
+        <f>Events!J28</f>
         <v>46130</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <f>Events!B21</f>
+        <f>Events!B29</f>
         <v>SÍ</v>
       </c>
       <c r="B29" s="4">
-        <f>Events!J21</f>
+        <f>Events!J29</f>
         <v>46131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <f>Events!B22</f>
+        <f>Events!B30</f>
         <v>KP</v>
       </c>
       <c r="B30" s="4">
-        <f>Events!J22</f>
+        <f>Events!J30</f>
         <v>46131</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B31" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
+        <f>Events!B31</f>
+        <v>Barna dans</v>
+      </c>
+      <c r="B31" s="4">
+        <f>Events!J31</f>
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>Events!B23</f>
+        <f>Events!B32</f>
         <v>UpT</v>
       </c>
       <c r="B32" s="4">
-        <f>Events!J23</f>
+        <f>Events!J32</f>
         <v>46134</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>Events!B24</f>
+        <f>Events!B33</f>
         <v>LR</v>
       </c>
       <c r="B33" s="4">
-        <f>Events!J24</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="str">
-        <f>Events!B25</f>
-        <v>FB</v>
-      </c>
-      <c r="B34" s="4">
-        <f>Events!J25</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="str">
-        <f>Events!B26</f>
-        <v>FB</v>
-      </c>
-      <c r="B35" s="4">
-        <f>Events!J26</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="str">
-        <f>Events!B27</f>
-        <v>SR</v>
-      </c>
-      <c r="B36" s="4">
-        <f>Events!J27</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="str">
-        <f>Events!B28</f>
-        <v>HT</v>
-      </c>
-      <c r="B37" s="4">
-        <f>Events!J28</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="str">
-        <f>Events!B29</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B38" s="4">
-        <f>Events!J29</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="str">
-        <f>Events!B30</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B39" s="4">
-        <f>Events!J30</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="str">
-        <f>Events!B31</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B40" s="4">
-        <f>Events!J31</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B41" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="str">
-        <f>Events!B32</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B42" s="4">
-        <f>Events!J32</f>
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="str">
-        <f>Events!B33</f>
-        <v>DP</v>
-      </c>
-      <c r="B43" s="4">
         <f>Events!J33</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="str">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
         <f>Events!B34</f>
-        <v>VR</v>
-      </c>
-      <c r="B44" s="4">
+        <v>FB</v>
+      </c>
+      <c r="B34" s="4">
         <f>Events!J34</f>
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="str">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
         <f>Events!B35</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B45" s="4">
+        <v>FB</v>
+      </c>
+      <c r="B35" s="4">
         <f>Events!J35</f>
         <v>46142</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="str">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
         <f>Events!B36</f>
         <v>SR</v>
       </c>
+      <c r="B36" s="4">
+        <f>Events!J36</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>Events!B37</f>
+        <v>HT</v>
+      </c>
+      <c r="B37" s="4">
+        <f>Events!J37</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
+        <f>Events!B38</f>
+        <v>K&amp;B</v>
+      </c>
+      <c r="B38" s="4">
+        <f>Events!J38</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f>Events!B39</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B39" s="4">
+        <f>Events!J39</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>Events!B40</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B40" s="4">
+        <f>Events!J40</f>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="str">
+        <f>Events!B41</f>
+        <v>KV</v>
+      </c>
+      <c r="B41" s="4">
+        <f>Events!J41</f>
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>Events!B42</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B42" s="4">
+        <f>Events!J42</f>
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>Events!B43</f>
+        <v>DP</v>
+      </c>
+      <c r="B43" s="4">
+        <f>Events!J43</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>Events!B44</f>
+        <v>VR</v>
+      </c>
+      <c r="B44" s="4">
+        <f>Events!J44</f>
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>Events!B45</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B45" s="4">
+        <f>Events!J45</f>
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>Events!B46</f>
+        <v>SR</v>
+      </c>
       <c r="B46" s="4">
-        <f>Events!J36</f>
+        <f>Events!J46</f>
         <v>46136</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
     </row>
   </sheetData>
@@ -5296,25 +5182,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5323,9 +5209,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -5334,9 +5220,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -5345,9 +5231,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -5356,9 +5242,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -5367,9 +5253,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5379,9 +5265,9 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5390,9 +5276,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -5401,9 +5287,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -5412,9 +5298,9 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -5423,9 +5309,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -5434,7 +5320,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5445,7 +5331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5456,7 +5342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5467,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5478,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5489,7 +5375,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5500,7 +5386,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5511,9 +5397,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5522,9 +5408,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5533,9 +5419,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5544,9 +5430,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5555,9 +5441,9 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5566,9 +5452,9 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5577,9 +5463,9 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5588,9 +5474,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5600,9 +5486,9 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5612,9 +5498,9 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5624,9 +5510,9 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5635,9 +5521,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5646,20 +5532,20 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5668,9 +5554,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5679,9 +5565,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5690,9 +5576,9 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5709,25 +5595,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5735,10 +5621,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>-10000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5746,10 +5632,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-10000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5760,7 +5646,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5771,7 +5657,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5782,7 +5668,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5793,7 +5679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5804,7 +5690,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5815,7 +5701,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5832,499 +5718,186 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>80</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
       <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>80</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21">
-        <f>+C20*2</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22">
-        <f>+C21*2</f>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23">
-        <f>+C22*2</f>
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24">
-        <f>+C23*2</f>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>90</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>70</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>70</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
@@ -6341,18 +5914,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6364,18 +5937,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -6387,7 +5960,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6398,7 +5971,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6410,12 +5983,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -6433,18 +6006,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6456,18 +6029,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6479,12 +6052,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -6493,21 +6066,21 @@
         <v>80</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FE0954-795F-C745-AD58-8DE50FC0395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00656468-57BD-491C-952C-B2B6195E03EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26080" windowHeight="15360" firstSheet="1" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="146">
   <si>
     <t>Event</t>
   </si>
@@ -147,9 +148,123 @@
     <t>EventRanking</t>
   </si>
   <si>
+    <t>Mínus</t>
+  </si>
+  <si>
+    <t>Helgi, kominn með aðra helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 4 helgar</t>
+  </si>
+  <si>
+    <t>Helgi, var með helgi síðast</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 4 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 5 helgar</t>
+  </si>
+  <si>
+    <t>Salur</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Vika</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Hvað hún er löng</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Langar vaktir</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
+  </si>
+  <si>
+    <t>Með hverjum?</t>
+  </si>
+  <si>
     <t>Skillset</t>
   </si>
   <si>
+    <t>Ef þarf skillset 2 en þú ert 1</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 3</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert</t>
+  </si>
+  <si>
     <t>Upprás</t>
   </si>
   <si>
@@ -207,6 +322,12 @@
     <t>EmpSkillset</t>
   </si>
   <si>
+    <t>Ef þarf skillset 1 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
+  </si>
+  <si>
     <t>Req_this_shift</t>
   </si>
   <si>
@@ -330,9 +451,6 @@
     <t>IA</t>
   </si>
   <si>
-    <t>MÍT</t>
-  </si>
-  <si>
     <t>NB</t>
   </si>
   <si>
@@ -345,9 +463,6 @@
     <t>KP</t>
   </si>
   <si>
-    <t>Barna dans</t>
-  </si>
-  <si>
     <t>UpT</t>
   </si>
   <si>
@@ -361,9 +476,6 @@
   </si>
   <si>
     <t>HT</t>
-  </si>
-  <si>
-    <t>KV</t>
   </si>
   <si>
     <t>DP</t>
@@ -457,7 +569,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -792,18 +906,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="9" max="11" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -814,7 +928,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -841,7 +955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -849,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -857,11 +971,11 @@
       </c>
       <c r="E2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>KL</v>
       </c>
       <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -885,12 +999,12 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -912,7 +1026,7 @@
       </c>
       <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -927,12 +1041,12 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -958,7 +1072,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4">
         <v>46113</v>
@@ -970,12 +1084,12 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -997,7 +1111,7 @@
       </c>
       <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1012,12 +1126,12 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -1043,7 +1157,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4">
         <v>46114</v>
@@ -1055,12 +1169,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
@@ -1086,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4">
         <v>46116</v>
@@ -1098,7 +1212,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1114,7 +1228,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1142,7 +1256,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1158,7 +1272,7 @@
       </c>
       <c r="E9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1186,7 +1300,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1202,7 +1316,7 @@
       </c>
       <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1229,7 +1343,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1245,7 +1359,7 @@
       </c>
       <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1272,12 +1386,12 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1288,7 +1402,7 @@
       </c>
       <c r="E12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1314,12 +1428,12 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -1330,7 +1444,7 @@
       </c>
       <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1357,7 +1471,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1384,7 +1498,7 @@
       </c>
       <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -1399,12 +1513,12 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -1415,7 +1529,7 @@
       </c>
       <c r="E15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1442,7 +1556,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1458,7 +1572,7 @@
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1486,12 +1600,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -1510,14 +1624,14 @@
       </c>
       <c r="G17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4">
         <v>46127</v>
@@ -1529,7 +1643,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1545,7 +1659,7 @@
       </c>
       <c r="E18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1573,15 +1687,15 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1589,41 +1703,42 @@
       </c>
       <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="K19" s="5">
-        <v>0.6875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L19" s="5">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1631,38 +1746,39 @@
       </c>
       <c r="E20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="K20" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="L20" s="5">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -1684,30 +1800,30 @@
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="K21" s="5">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="L21" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1715,41 +1831,42 @@
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="K22" s="5">
-        <v>0.625</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1761,37 +1878,37 @@
       </c>
       <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" s="4">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="K23" s="5">
         <v>0.66666666666666663</v>
       </c>
       <c r="L23" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1803,38 +1920,37 @@
       </c>
       <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G24">
-        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4">
-        <v>46129</v>
+        <v>46137</v>
       </c>
       <c r="K24" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L24" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1846,38 +1962,37 @@
       </c>
       <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G25">
-        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="4">
-        <v>46130</v>
+        <v>46141</v>
       </c>
       <c r="K25" s="5">
-        <v>0.41666666666666669</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L25" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1889,38 +2004,37 @@
       </c>
       <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G26">
-        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="4">
-        <v>46130</v>
+        <v>46142</v>
       </c>
       <c r="K26" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L26" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1928,89 +2042,89 @@
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>KL</v>
       </c>
       <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="K27" s="5">
         <v>0.79166666666666663</v>
       </c>
       <c r="L27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>KL</v>
       </c>
       <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="K28" s="5">
-        <v>0.47916666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="L28" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2018,9 +2132,10 @@
       </c>
       <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
@@ -2031,110 +2146,110 @@
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="K29" s="5">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>BL</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="K30" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L30" s="5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
+        <v>BL</v>
       </c>
       <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="K31" s="5">
-        <v>0.6875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L31" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2142,83 +2257,85 @@
       </c>
       <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="K32" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="L32" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Party</v>
       </c>
       <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4">
         <v>46137</v>
       </c>
       <c r="K33" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L33" s="5">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2226,41 +2343,41 @@
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4">
-        <v>46141</v>
+        <v>46138</v>
       </c>
       <c r="K34" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L34" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2268,41 +2385,42 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>EB</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
       </c>
       <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4">
         <v>46142</v>
       </c>
       <c r="K35" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="L35" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2314,454 +2432,25 @@
       </c>
       <c r="F36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G36">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H36">
-        <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" s="4">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="K36" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" t="str">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
-      </c>
-      <c r="F37" t="str">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37" s="4">
-        <v>46137</v>
-      </c>
-      <c r="K37" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L37" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" t="str">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
-      </c>
-      <c r="E38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F38" t="str">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I38">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4">
-        <v>46137</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" t="str">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F39" t="str">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39" s="4">
-        <v>46134</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L39" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>40</v>
-      </c>
-      <c r="B40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" t="str">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
-      </c>
-      <c r="E40">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F40" t="str">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="G40">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40" s="4">
-        <v>46141</v>
-      </c>
-      <c r="K40" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="L40" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" t="str">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F41" t="str">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="G41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4">
-        <v>46132</v>
-      </c>
-      <c r="K41" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L41" s="5">
         <v>0.875</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>42</v>
-      </c>
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" t="str">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E42">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F42" t="str">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G42">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I42">
-        <v>7</v>
-      </c>
-      <c r="J42" s="4">
-        <v>46136</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L42" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Party</v>
-      </c>
-      <c r="E43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
-      </c>
-      <c r="F43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>6</v>
-      </c>
-      <c r="I43">
-        <v>12</v>
-      </c>
-      <c r="J43" s="4">
-        <v>46137</v>
-      </c>
-      <c r="K43" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L43" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>44</v>
-      </c>
-      <c r="B44" t="s">
-        <v>101</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" t="str">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E44">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
-      </c>
-      <c r="F44" t="str">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <f>_xlfn.XLOOKUP(C44,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I44">
-        <v>8</v>
-      </c>
-      <c r="J44" s="4">
-        <v>46138</v>
-      </c>
-      <c r="K44" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L44" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>45</v>
-      </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" t="str">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E45">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F45" t="str">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="G45">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <f>_xlfn.XLOOKUP(C45,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I45">
-        <v>11</v>
-      </c>
-      <c r="J45" s="4">
-        <v>46142</v>
-      </c>
-      <c r="K45" s="5">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="L45" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" t="str">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E46">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F46" t="str">
-        <f>_xlfn.XLOOKUP(C46,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>4</v>
-      </c>
-      <c r="J46" s="4">
-        <v>46136</v>
-      </c>
-      <c r="K46" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L46" s="5">
-        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -2774,7 +2463,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C46</xm:sqref>
+          <xm:sqref>C2:C36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2785,470 +2474,470 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3261,16 +2950,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
-  <dimension ref="A1:AF43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AH43"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="31" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2">
         <v>46113</v>
@@ -3363,8 +3054,9 @@
         <v>46142</v>
       </c>
       <c r="AF1" s="2"/>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH1" s="2"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3459,7 +3151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3485,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3499,12 +3191,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3533,7 +3225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3628,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3723,12 +3415,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3739,12 +3431,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3791,17 +3483,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3836,12 +3528,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3864,12 +3556,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3934,12 +3626,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3953,7 +3645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4048,12 +3740,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4130,7 +3822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4171,7 +3863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4266,12 +3958,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4294,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4317,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4343,27 +4035,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4458,17 +4150,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4476,17 +4168,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4521,12 +4213,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:31" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4535,13 +4227,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4715,7 +4407,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
@@ -4725,7 +4417,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
@@ -4735,7 +4427,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
@@ -4745,7 +4437,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
@@ -4755,7 +4447,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
@@ -4765,7 +4457,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
@@ -4775,7 +4467,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
@@ -4785,7 +4477,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
@@ -4795,7 +4487,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4805,7 +4497,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4815,7 +4507,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
@@ -4825,7 +4517,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
@@ -4835,7 +4527,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
@@ -4845,7 +4537,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
@@ -4855,7 +4547,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
@@ -4865,7 +4557,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>IA</v>
@@ -4875,7 +4567,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Sinfó</v>
@@ -4885,293 +4577,293 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="str">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B19" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B20" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B21" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B22" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B23" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B24" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B25" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B26" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="str">
         <f>Events!B19</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B19" s="4">
+        <v>NB</v>
+      </c>
+      <c r="B27" s="4">
         <f>Events!J19</f>
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="str">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="str">
         <f>Events!B20</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B20" s="4">
+        <v>DWC</v>
+      </c>
+      <c r="B28" s="4">
         <f>Events!J20</f>
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="str">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="str">
         <f>Events!B21</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B21" s="4">
+        <v>SÍ</v>
+      </c>
+      <c r="B29" s="4">
         <f>Events!J21</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="str">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="str">
         <f>Events!B22</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B22" s="4">
+        <v>KP</v>
+      </c>
+      <c r="B30" s="4">
         <f>Events!J22</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="str">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B31" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="str">
         <f>Events!B23</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B23" s="4">
+        <v>UpT</v>
+      </c>
+      <c r="B32" s="4">
         <f>Events!J23</f>
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="str">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="str">
         <f>Events!B24</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B24" s="4">
+        <v>LR</v>
+      </c>
+      <c r="B33" s="4">
         <f>Events!J24</f>
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="str">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="str">
         <f>Events!B25</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B25" s="4">
+        <v>FB</v>
+      </c>
+      <c r="B34" s="4">
         <f>Events!J25</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="str">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="str">
         <f>Events!B26</f>
-        <v>MÍT</v>
-      </c>
-      <c r="B26" s="4">
+        <v>FB</v>
+      </c>
+      <c r="B35" s="4">
         <f>Events!J26</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="str">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="str">
         <f>Events!B27</f>
-        <v>NB</v>
-      </c>
-      <c r="B27" s="4">
+        <v>SR</v>
+      </c>
+      <c r="B36" s="4">
         <f>Events!J27</f>
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="str">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="str">
         <f>Events!B28</f>
-        <v>DWC</v>
-      </c>
-      <c r="B28" s="4">
+        <v>HT</v>
+      </c>
+      <c r="B37" s="4">
         <f>Events!J28</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="str">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="str">
         <f>Events!B29</f>
-        <v>SÍ</v>
-      </c>
-      <c r="B29" s="4">
+        <v>K&amp;B</v>
+      </c>
+      <c r="B38" s="4">
         <f>Events!J29</f>
-        <v>46131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="str">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="str">
         <f>Events!B30</f>
-        <v>KP</v>
-      </c>
-      <c r="B30" s="4">
+        <v>Múlinn</v>
+      </c>
+      <c r="B39" s="4">
         <f>Events!J30</f>
-        <v>46131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="str">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="str">
         <f>Events!B31</f>
-        <v>Barna dans</v>
-      </c>
-      <c r="B31" s="4">
+        <v>Múlinn</v>
+      </c>
+      <c r="B40" s="4">
         <f>Events!J31</f>
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="str">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B41" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="str">
         <f>Events!B32</f>
-        <v>UpT</v>
-      </c>
-      <c r="B32" s="4">
+        <v>Sinfó</v>
+      </c>
+      <c r="B42" s="4">
         <f>Events!J32</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="str">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="str">
         <f>Events!B33</f>
-        <v>LR</v>
-      </c>
-      <c r="B33" s="4">
+        <v>DP</v>
+      </c>
+      <c r="B43" s="4">
         <f>Events!J33</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="str">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="str">
         <f>Events!B34</f>
-        <v>FB</v>
-      </c>
-      <c r="B34" s="4">
+        <v>VR</v>
+      </c>
+      <c r="B44" s="4">
         <f>Events!J34</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="str">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="str">
         <f>Events!B35</f>
-        <v>FB</v>
-      </c>
-      <c r="B35" s="4">
+        <v>Sinfó</v>
+      </c>
+      <c r="B45" s="4">
         <f>Events!J35</f>
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="str">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="str">
         <f>Events!B36</f>
         <v>SR</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B46" s="4">
         <f>Events!J36</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="str">
-        <f>Events!B37</f>
-        <v>HT</v>
-      </c>
-      <c r="B37" s="4">
-        <f>Events!J37</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="str">
-        <f>Events!B38</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B38" s="4">
-        <f>Events!J38</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="str">
-        <f>Events!B39</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B39" s="4">
-        <f>Events!J39</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="str">
-        <f>Events!B40</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B40" s="4">
-        <f>Events!J40</f>
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="str">
-        <f>Events!B41</f>
-        <v>KV</v>
-      </c>
-      <c r="B41" s="4">
-        <f>Events!J41</f>
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="str">
-        <f>Events!B42</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B42" s="4">
-        <f>Events!J42</f>
         <v>46136</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="str">
-        <f>Events!B43</f>
-        <v>DP</v>
-      </c>
-      <c r="B43" s="4">
-        <f>Events!J43</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="str">
-        <f>Events!B44</f>
-        <v>VR</v>
-      </c>
-      <c r="B44" s="4">
-        <f>Events!J44</f>
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="str">
-        <f>Events!B45</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B45" s="4">
-        <f>Events!J45</f>
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="str">
-        <f>Events!B46</f>
-        <v>SR</v>
-      </c>
-      <c r="B46" s="4">
-        <f>Events!J46</f>
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="4"/>
     </row>
   </sheetData>
@@ -5182,25 +4874,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5209,9 +4901,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -5220,9 +4912,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -5231,9 +4923,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -5242,9 +4934,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -5253,9 +4945,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5265,9 +4957,9 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5276,9 +4968,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -5287,9 +4979,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -5298,9 +4990,9 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -5309,9 +5001,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -5320,7 +5012,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5331,7 +5023,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5342,7 +5034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5353,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5364,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5375,7 +5067,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5386,7 +5078,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5397,9 +5089,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5408,9 +5100,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5419,9 +5111,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5430,9 +5122,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5441,9 +5133,9 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5452,9 +5144,9 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5463,9 +5155,9 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5474,9 +5166,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5486,9 +5178,9 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5498,9 +5190,9 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5510,9 +5202,9 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5521,9 +5213,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5532,20 +5224,20 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5554,9 +5246,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5565,9 +5257,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5576,9 +5268,9 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5595,25 +5287,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5621,10 +5313,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5632,10 +5324,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5646,7 +5338,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5657,7 +5349,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5668,7 +5360,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5679,7 +5371,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5690,7 +5382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5701,7 +5393,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5718,24 +5410,337 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21">
+        <f>+C20*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <f>+C21*2</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <f>+C22*2</f>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <f>+C23*2</f>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5753,18 +5758,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5776,12 +5781,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -5799,12 +5804,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -5822,18 +5827,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5845,12 +5850,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -5868,12 +5873,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -5891,12 +5896,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -5914,18 +5919,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5937,18 +5942,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5960,7 +5965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5971,7 +5976,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5983,12 +5988,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -6006,18 +6011,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
       </c>
       <c r="D13">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6029,18 +6034,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6052,12 +6057,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -6066,21 +6071,21 @@
         <v>80</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/04_26.xlsx
+++ b/Data/04_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00656468-57BD-491C-952C-B2B6195E03EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{280E08BD-264A-46E2-BEE2-435F84A28306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
   <si>
     <t>Event</t>
   </si>
@@ -907,17 +907,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="9" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -955,7 +955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -999,7 +999,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2474,14 +2474,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2951,15 +2951,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AH43"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="31" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="31" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
@@ -3056,7 +3056,7 @@
       <c r="AF1" s="2"/>
       <c r="AH1" s="2"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3191,12 +3191,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3415,12 +3415,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3431,12 +3431,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3483,17 +3483,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3528,12 +3528,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3556,12 +3556,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3626,12 +3626,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3740,12 +3740,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3958,12 +3958,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4035,27 +4035,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4150,17 +4150,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4168,17 +4168,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4213,12 +4213,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4227,13 +4227,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ49"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4407,7 +4407,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
@@ -4417,7 +4417,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
@@ -4427,7 +4427,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
@@ -4437,7 +4437,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
@@ -4447,7 +4447,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
@@ -4457,7 +4457,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
@@ -4467,7 +4467,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
@@ -4477,7 +4477,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
@@ -4487,7 +4487,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4497,7 +4497,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4507,7 +4507,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
@@ -4517,7 +4517,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
@@ -4527,7 +4527,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
@@ -4537,7 +4537,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
@@ -4547,7 +4547,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
@@ -4557,7 +4557,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>IA</v>
@@ -4567,7 +4567,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Sinfó</v>
@@ -4577,7 +4577,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4587,7 +4587,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4597,7 +4597,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4607,7 +4607,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4617,7 +4617,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4627,7 +4627,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4637,7 +4637,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4647,7 +4647,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4657,7 +4657,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B19</f>
         <v>NB</v>
@@ -4667,7 +4667,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B20</f>
         <v>DWC</v>
@@ -4677,7 +4677,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B21</f>
         <v>SÍ</v>
@@ -4687,7 +4687,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B22</f>
         <v>KP</v>
@@ -4697,7 +4697,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4707,7 +4707,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>Events!B23</f>
         <v>UpT</v>
@@ -4717,7 +4717,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>Events!B24</f>
         <v>LR</v>
@@ -4727,7 +4727,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>Events!B25</f>
         <v>FB</v>
@@ -4737,7 +4737,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>Events!B26</f>
         <v>FB</v>
@@ -4747,7 +4747,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>Events!B27</f>
         <v>SR</v>
@@ -4757,7 +4757,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>Events!B28</f>
         <v>HT</v>
@@ -4767,7 +4767,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>Events!B29</f>
         <v>K&amp;B</v>
@@ -4777,7 +4777,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>Events!B30</f>
         <v>Múlinn</v>
@@ -4787,7 +4787,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4797,7 +4797,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="e">
         <f>Events!#REF!</f>
         <v>#REF!</v>
@@ -4807,7 +4807,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>Events!B32</f>
         <v>Sinfó</v>
@@ -4817,7 +4817,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>Events!B33</f>
         <v>DP</v>
@@ -4827,7 +4827,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="str">
         <f>Events!B34</f>
         <v>VR</v>
@@ -4837,7 +4837,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>Events!B35</f>
         <v>Sinfó</v>
@@ -4847,7 +4847,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>Events!B36</f>
         <v>SR</v>
@@ -4857,13 +4857,13 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="4"/>
     </row>
   </sheetData>
@@ -4873,13 +4873,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>78</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5078,204 +5078,193 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>80</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>80</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>80</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>80</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>80</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>81</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <f>+C25*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>81</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>81</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>88</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>88</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>88</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>88</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36">
-        <v>4</v>
-      </c>
-      <c r="C36">
         <v>-100</v>
       </c>
     </row>
@@ -5287,14 +5276,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
@@ -5305,7 +5294,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5316,7 +5305,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5327,7 +5316,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5338,7 +5327,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5349,7 +5338,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5360,7 +5349,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5371,7 +5360,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5382,7 +5371,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5393,7 +5382,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5412,20 +5401,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -5436,7 +5425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -5444,7 +5433,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -5452,7 +5441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>32</v>
       </c>
@@ -5460,7 +5449,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -5468,7 +5457,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -5479,7 +5468,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -5487,7 +5476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>37</v>
       </c>
@@ -5495,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -5503,7 +5492,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -5511,7 +5500,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -5522,7 +5511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>42</v>
       </c>
@@ -5530,7 +5519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>43</v>
       </c>
@@ -5538,7 +5527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>44</v>
       </c>
@@ -5546,7 +5535,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>45</v>
       </c>
@@ -5554,7 +5543,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -5565,7 +5554,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>48</v>
       </c>
@@ -5574,7 +5563,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>49</v>
       </c>
@@ -5583,7 +5572,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>50</v>
       </c>
@@ -5592,7 +5581,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>51</v>
       </c>
@@ -5601,7 +5590,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -5612,7 +5601,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>54</v>
       </c>
@@ -5621,7 +5610,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>55</v>
       </c>
@@ -5630,7 +5619,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>56</v>
       </c>
@@ -5639,7 +5628,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -5650,12 +5639,12 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -5666,7 +5655,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>62</v>
       </c>
@@ -5674,7 +5663,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>61</v>
       </c>
@@ -5682,7 +5671,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>65</v>
       </c>
@@ -5690,7 +5679,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>64</v>
       </c>
@@ -5698,7 +5687,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>63</v>
       </c>
@@ -5706,7 +5695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>86</v>
       </c>
@@ -5725,17 +5714,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5758,7 +5747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5781,7 +5770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5804,7 +5793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5827,7 +5816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5850,7 +5839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5873,7 +5862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5896,7 +5885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5919,7 +5908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5942,7 +5931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5965,7 +5954,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5988,7 +5977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -6011,7 +6000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6034,7 +6023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -6057,7 +6046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6080,7 +6069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
